--- a/data/unit-data.xlsx
+++ b/data/unit-data.xlsx
@@ -7,16 +7,16 @@
     <workbookView xWindow="480" yWindow="24" windowWidth="22056" windowHeight="9264"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="unit_rules" sheetId="1" r:id="rId1"/>
+    <sheet name="dong_meta" sheetId="2" r:id="rId2"/>
+    <sheet name="unit_exceptions" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="39">
   <si>
     <t>dong</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,10 +39,6 @@
   </si>
   <si>
     <t>loan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>saletype</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -94,6 +90,86 @@
   </si>
   <si>
     <t>contract2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dong</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>floor_min</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>floor_max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>line_list</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dong</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ho</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>status</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>message</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blocked</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101동 1층 3호 라인은 부대시설입니다. 다른 호실을 입력해 주세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>105동 1층 2호 라인은 부대시설입니다. 다른 호실을 입력해 주세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>105동 2층 2호 라인은 부대시설입니다. 다른 호실을 입력해 주세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>styletype</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>calc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>84A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6~16층</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -445,9 +521,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N148"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
+    <col min="3" max="3" width="8.69921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.09765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.3984375" bestFit="1" customWidth="1"/>
@@ -468,13 +545,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
@@ -486,22 +563,22 @@
         <v>4</v>
       </c>
       <c r="I1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" t="s">
         <v>17</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>18</v>
-      </c>
-      <c r="K1" t="s">
-        <v>19</v>
       </c>
       <c r="L1" t="s">
         <v>5</v>
       </c>
       <c r="M1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" t="s">
         <v>8</v>
-      </c>
-      <c r="N1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
@@ -509,16 +586,16 @@
         <v>101</v>
       </c>
       <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
         <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
@@ -526,16 +603,16 @@
         <v>102</v>
       </c>
       <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
         <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
@@ -546,10 +623,10 @@
         <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>363000000</v>
@@ -571,7 +648,7 @@
         <v>217800000</v>
       </c>
       <c r="M4">
-        <f>SUM(G4-L4-I4-J4)</f>
+        <f>SUM(G4-L4-I4-K4)</f>
         <v>115200000</v>
       </c>
       <c r="N4">
@@ -587,10 +664,10 @@
         <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>363000000</v>
@@ -602,6 +679,9 @@
         <v>10000000</v>
       </c>
       <c r="J5">
+        <v>20000000</v>
+      </c>
+      <c r="K5">
         <v>20000000</v>
       </c>
       <c r="L5">
@@ -609,7 +689,7 @@
         <v>217800000</v>
       </c>
       <c r="M5">
-        <f t="shared" ref="M5:M13" si="1">SUM(G5-L5-I5-J5)</f>
+        <f t="shared" ref="M5:M13" si="1">SUM(G5-L5-I5-K5)</f>
         <v>115200000</v>
       </c>
       <c r="N5">
@@ -625,10 +705,10 @@
         <v>201</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>374000000</v>
@@ -640,6 +720,9 @@
         <v>10000000</v>
       </c>
       <c r="J6">
+        <v>20000000</v>
+      </c>
+      <c r="K6">
         <v>20000000</v>
       </c>
       <c r="L6">
@@ -663,10 +746,10 @@
         <v>202</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>374000000</v>
@@ -678,6 +761,9 @@
         <v>10000000</v>
       </c>
       <c r="J7">
+        <v>20000000</v>
+      </c>
+      <c r="K7">
         <v>20000000</v>
       </c>
       <c r="L7">
@@ -701,10 +787,10 @@
         <v>301</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>374000000</v>
@@ -716,6 +802,9 @@
         <v>10000000</v>
       </c>
       <c r="J8">
+        <v>20000000</v>
+      </c>
+      <c r="K8">
         <v>20000000</v>
       </c>
       <c r="L8">
@@ -739,10 +828,10 @@
         <v>302</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>374000000</v>
@@ -754,6 +843,9 @@
         <v>10000000</v>
       </c>
       <c r="J9">
+        <v>20000000</v>
+      </c>
+      <c r="K9">
         <v>20000000</v>
       </c>
       <c r="L9">
@@ -777,10 +869,10 @@
         <v>401</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>382000000</v>
@@ -792,6 +884,9 @@
         <v>10000000</v>
       </c>
       <c r="J10">
+        <v>20000000</v>
+      </c>
+      <c r="K10">
         <v>20000000</v>
       </c>
       <c r="L10">
@@ -815,10 +910,10 @@
         <v>402</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>382000000</v>
@@ -830,6 +925,9 @@
         <v>10000000</v>
       </c>
       <c r="J11">
+        <v>20000000</v>
+      </c>
+      <c r="K11">
         <v>20000000</v>
       </c>
       <c r="L11">
@@ -853,10 +951,10 @@
         <v>501</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>382000000</v>
@@ -868,6 +966,9 @@
         <v>10000000</v>
       </c>
       <c r="J12">
+        <v>20000000</v>
+      </c>
+      <c r="K12">
         <v>20000000</v>
       </c>
       <c r="L12">
@@ -891,10 +992,10 @@
         <v>502</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>382000000</v>
@@ -906,6 +1007,9 @@
         <v>10000000</v>
       </c>
       <c r="J13">
+        <v>20000000</v>
+      </c>
+      <c r="K13">
         <v>20000000</v>
       </c>
       <c r="L13">
@@ -926,16 +1030,16 @@
         <v>103</v>
       </c>
       <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
         <v>10</v>
-      </c>
-      <c r="D14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.4">
@@ -946,10 +1050,10 @@
         <v>1701</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>390000000</v>
@@ -967,15 +1071,15 @@
         <v>20000000</v>
       </c>
       <c r="L15">
-        <f t="shared" ref="L15:L34" si="3">SUM(G15*60%)</f>
+        <f t="shared" ref="L15:L56" si="3">SUM(G15*60%)</f>
         <v>234000000</v>
       </c>
       <c r="M15">
-        <f t="shared" ref="M15:M34" si="4">SUM(G15-L15-I15-J15)</f>
+        <f t="shared" ref="M15:M54" si="4">SUM(G15-L15-I15-K15)</f>
         <v>126000000</v>
       </c>
       <c r="N15">
-        <f t="shared" ref="N15:N34" si="5">SUM(G15-L15)</f>
+        <f t="shared" ref="N15:N56" si="5">SUM(G15-L15)</f>
         <v>156000000</v>
       </c>
     </row>
@@ -987,10 +1091,10 @@
         <v>1702</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>390000000</v>
@@ -1028,10 +1132,10 @@
         <v>1801</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>390000000</v>
@@ -1069,10 +1173,10 @@
         <v>1802</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>390000000</v>
@@ -1110,10 +1214,10 @@
         <v>1901</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>390000000</v>
@@ -1151,10 +1255,10 @@
         <v>1902</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>390000000</v>
@@ -1192,10 +1296,10 @@
         <v>2001</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>390000000</v>
@@ -1233,10 +1337,10 @@
         <v>2002</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G22">
         <v>390000000</v>
@@ -1274,10 +1378,10 @@
         <v>2101</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>397000000</v>
@@ -1315,10 +1419,10 @@
         <v>2102</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <v>397000000</v>
@@ -1356,10 +1460,10 @@
         <v>2201</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>397000000</v>
@@ -1397,10 +1501,10 @@
         <v>2202</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>397000000</v>
@@ -1438,10 +1542,10 @@
         <v>2301</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>397000000</v>
@@ -1479,10 +1583,10 @@
         <v>2302</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>397000000</v>
@@ -1520,10 +1624,10 @@
         <v>2401</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G29">
         <v>397000000</v>
@@ -1561,10 +1665,10 @@
         <v>2402</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>397000000</v>
@@ -1602,10 +1706,10 @@
         <v>2501</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>397000000</v>
@@ -1643,10 +1747,10 @@
         <v>2502</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G32">
         <v>397000000</v>
@@ -1684,10 +1788,10 @@
         <v>2601</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G33">
         <v>397000000</v>
@@ -1725,10 +1829,10 @@
         <v>2602</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G34">
         <v>397000000</v>
@@ -1755,6 +1859,4629 @@
       </c>
       <c r="N34">
         <f t="shared" si="5"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A35">
+        <v>104</v>
+      </c>
+      <c r="B35">
+        <v>101</v>
+      </c>
+      <c r="C35" t="s">
+        <v>35</v>
+      </c>
+      <c r="F35" t="s">
+        <v>36</v>
+      </c>
+      <c r="G35">
+        <v>363000000</v>
+      </c>
+      <c r="H35">
+        <v>525000000</v>
+      </c>
+      <c r="I35">
+        <v>10000000</v>
+      </c>
+      <c r="J35">
+        <v>20000000</v>
+      </c>
+      <c r="K35">
+        <v>20000000</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="3"/>
+        <v>217800000</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="4"/>
+        <v>115200000</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="5"/>
+        <v>145200000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A36">
+        <v>104</v>
+      </c>
+      <c r="B36">
+        <v>102</v>
+      </c>
+      <c r="C36" t="s">
+        <v>35</v>
+      </c>
+      <c r="F36" t="s">
+        <v>36</v>
+      </c>
+      <c r="G36">
+        <v>363000000</v>
+      </c>
+      <c r="H36">
+        <v>525000000</v>
+      </c>
+      <c r="I36">
+        <v>10000000</v>
+      </c>
+      <c r="J36">
+        <v>20000000</v>
+      </c>
+      <c r="K36">
+        <v>20000000</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="3"/>
+        <v>217800000</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="4"/>
+        <v>115200000</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="5"/>
+        <v>145200000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A37">
+        <v>104</v>
+      </c>
+      <c r="B37">
+        <v>103</v>
+      </c>
+      <c r="C37" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" t="s">
+        <v>36</v>
+      </c>
+      <c r="G37">
+        <v>363000000</v>
+      </c>
+      <c r="H37">
+        <v>525000000</v>
+      </c>
+      <c r="I37">
+        <v>10000000</v>
+      </c>
+      <c r="J37">
+        <v>20000000</v>
+      </c>
+      <c r="K37">
+        <v>20000000</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="3"/>
+        <v>217800000</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="4"/>
+        <v>115200000</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="5"/>
+        <v>145200000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A38">
+        <v>104</v>
+      </c>
+      <c r="B38">
+        <v>104</v>
+      </c>
+      <c r="C38" t="s">
+        <v>35</v>
+      </c>
+      <c r="F38" t="s">
+        <v>36</v>
+      </c>
+      <c r="G38">
+        <v>363000000</v>
+      </c>
+      <c r="H38">
+        <v>525000000</v>
+      </c>
+      <c r="I38">
+        <v>10000000</v>
+      </c>
+      <c r="J38">
+        <v>20000000</v>
+      </c>
+      <c r="K38">
+        <v>20000000</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="3"/>
+        <v>217800000</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="4"/>
+        <v>115200000</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="5"/>
+        <v>145200000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A39">
+        <v>104</v>
+      </c>
+      <c r="B39">
+        <v>201</v>
+      </c>
+      <c r="C39" t="s">
+        <v>35</v>
+      </c>
+      <c r="F39" t="s">
+        <v>36</v>
+      </c>
+      <c r="G39">
+        <v>374000000</v>
+      </c>
+      <c r="H39">
+        <v>530000000</v>
+      </c>
+      <c r="I39">
+        <v>10000000</v>
+      </c>
+      <c r="J39">
+        <v>20000000</v>
+      </c>
+      <c r="K39">
+        <v>20000000</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="3"/>
+        <v>224400000</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="4"/>
+        <v>119600000</v>
+      </c>
+      <c r="N39">
+        <f t="shared" si="5"/>
+        <v>149600000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A40">
+        <v>104</v>
+      </c>
+      <c r="B40">
+        <v>202</v>
+      </c>
+      <c r="C40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F40" t="s">
+        <v>36</v>
+      </c>
+      <c r="G40">
+        <v>374000000</v>
+      </c>
+      <c r="H40">
+        <v>530000000</v>
+      </c>
+      <c r="I40">
+        <v>10000000</v>
+      </c>
+      <c r="J40">
+        <v>20000000</v>
+      </c>
+      <c r="K40">
+        <v>20000000</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="3"/>
+        <v>224400000</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="4"/>
+        <v>119600000</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="5"/>
+        <v>149600000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A41">
+        <v>104</v>
+      </c>
+      <c r="B41">
+        <v>203</v>
+      </c>
+      <c r="C41" t="s">
+        <v>35</v>
+      </c>
+      <c r="F41" t="s">
+        <v>36</v>
+      </c>
+      <c r="G41">
+        <v>374000000</v>
+      </c>
+      <c r="H41">
+        <v>530000000</v>
+      </c>
+      <c r="I41">
+        <v>10000000</v>
+      </c>
+      <c r="J41">
+        <v>20000000</v>
+      </c>
+      <c r="K41">
+        <v>20000000</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="3"/>
+        <v>224400000</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="4"/>
+        <v>119600000</v>
+      </c>
+      <c r="N41">
+        <f t="shared" si="5"/>
+        <v>149600000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A42">
+        <v>104</v>
+      </c>
+      <c r="B42">
+        <v>204</v>
+      </c>
+      <c r="C42" t="s">
+        <v>35</v>
+      </c>
+      <c r="F42" t="s">
+        <v>36</v>
+      </c>
+      <c r="G42">
+        <v>374000000</v>
+      </c>
+      <c r="H42">
+        <v>530000000</v>
+      </c>
+      <c r="I42">
+        <v>10000000</v>
+      </c>
+      <c r="J42">
+        <v>20000000</v>
+      </c>
+      <c r="K42">
+        <v>20000000</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="3"/>
+        <v>224400000</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="4"/>
+        <v>119600000</v>
+      </c>
+      <c r="N42">
+        <f t="shared" si="5"/>
+        <v>149600000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A43">
+        <v>104</v>
+      </c>
+      <c r="B43">
+        <v>301</v>
+      </c>
+      <c r="C43" t="s">
+        <v>35</v>
+      </c>
+      <c r="F43" t="s">
+        <v>36</v>
+      </c>
+      <c r="G43">
+        <v>374000000</v>
+      </c>
+      <c r="H43">
+        <v>535000000</v>
+      </c>
+      <c r="I43">
+        <v>10000000</v>
+      </c>
+      <c r="J43">
+        <v>20000000</v>
+      </c>
+      <c r="K43">
+        <v>20000000</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="3"/>
+        <v>224400000</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="4"/>
+        <v>119600000</v>
+      </c>
+      <c r="N43">
+        <f t="shared" si="5"/>
+        <v>149600000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A44">
+        <v>104</v>
+      </c>
+      <c r="B44">
+        <v>302</v>
+      </c>
+      <c r="C44" t="s">
+        <v>35</v>
+      </c>
+      <c r="F44" t="s">
+        <v>36</v>
+      </c>
+      <c r="G44">
+        <v>374000000</v>
+      </c>
+      <c r="H44">
+        <v>535000000</v>
+      </c>
+      <c r="I44">
+        <v>10000000</v>
+      </c>
+      <c r="J44">
+        <v>20000000</v>
+      </c>
+      <c r="K44">
+        <v>20000000</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="3"/>
+        <v>224400000</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="4"/>
+        <v>119600000</v>
+      </c>
+      <c r="N44">
+        <f t="shared" si="5"/>
+        <v>149600000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A45">
+        <v>104</v>
+      </c>
+      <c r="B45">
+        <v>303</v>
+      </c>
+      <c r="C45" t="s">
+        <v>35</v>
+      </c>
+      <c r="F45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G45">
+        <v>374000000</v>
+      </c>
+      <c r="H45">
+        <v>535000000</v>
+      </c>
+      <c r="I45">
+        <v>10000000</v>
+      </c>
+      <c r="J45">
+        <v>20000000</v>
+      </c>
+      <c r="K45">
+        <v>20000000</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="3"/>
+        <v>224400000</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="4"/>
+        <v>119600000</v>
+      </c>
+      <c r="N45">
+        <f t="shared" si="5"/>
+        <v>149600000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A46">
+        <v>104</v>
+      </c>
+      <c r="B46">
+        <v>304</v>
+      </c>
+      <c r="C46" t="s">
+        <v>35</v>
+      </c>
+      <c r="F46" t="s">
+        <v>36</v>
+      </c>
+      <c r="G46">
+        <v>374000000</v>
+      </c>
+      <c r="H46">
+        <v>535000000</v>
+      </c>
+      <c r="I46">
+        <v>10000000</v>
+      </c>
+      <c r="J46">
+        <v>20000000</v>
+      </c>
+      <c r="K46">
+        <v>20000000</v>
+      </c>
+      <c r="L46">
+        <f t="shared" si="3"/>
+        <v>224400000</v>
+      </c>
+      <c r="M46">
+        <f t="shared" si="4"/>
+        <v>119600000</v>
+      </c>
+      <c r="N46">
+        <f t="shared" si="5"/>
+        <v>149600000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A47">
+        <v>104</v>
+      </c>
+      <c r="B47">
+        <v>401</v>
+      </c>
+      <c r="C47" t="s">
+        <v>35</v>
+      </c>
+      <c r="F47" t="s">
+        <v>36</v>
+      </c>
+      <c r="G47">
+        <v>382000000</v>
+      </c>
+      <c r="H47">
+        <v>540000000</v>
+      </c>
+      <c r="I47">
+        <v>10000000</v>
+      </c>
+      <c r="J47">
+        <v>20000000</v>
+      </c>
+      <c r="K47">
+        <v>20000000</v>
+      </c>
+      <c r="L47">
+        <f t="shared" si="3"/>
+        <v>229200000</v>
+      </c>
+      <c r="M47">
+        <f t="shared" si="4"/>
+        <v>122800000</v>
+      </c>
+      <c r="N47">
+        <f t="shared" si="5"/>
+        <v>152800000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A48">
+        <v>104</v>
+      </c>
+      <c r="B48">
+        <v>402</v>
+      </c>
+      <c r="C48" t="s">
+        <v>35</v>
+      </c>
+      <c r="F48" t="s">
+        <v>36</v>
+      </c>
+      <c r="G48">
+        <v>382000000</v>
+      </c>
+      <c r="H48">
+        <v>540000000</v>
+      </c>
+      <c r="I48">
+        <v>10000000</v>
+      </c>
+      <c r="J48">
+        <v>20000000</v>
+      </c>
+      <c r="K48">
+        <v>20000000</v>
+      </c>
+      <c r="L48">
+        <f t="shared" si="3"/>
+        <v>229200000</v>
+      </c>
+      <c r="M48">
+        <f t="shared" si="4"/>
+        <v>122800000</v>
+      </c>
+      <c r="N48">
+        <f t="shared" si="5"/>
+        <v>152800000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A49">
+        <v>104</v>
+      </c>
+      <c r="B49">
+        <v>403</v>
+      </c>
+      <c r="C49" t="s">
+        <v>35</v>
+      </c>
+      <c r="F49" t="s">
+        <v>36</v>
+      </c>
+      <c r="G49">
+        <v>382000000</v>
+      </c>
+      <c r="H49">
+        <v>540000000</v>
+      </c>
+      <c r="I49">
+        <v>10000000</v>
+      </c>
+      <c r="J49">
+        <v>20000000</v>
+      </c>
+      <c r="K49">
+        <v>20000000</v>
+      </c>
+      <c r="L49">
+        <f t="shared" si="3"/>
+        <v>229200000</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="4"/>
+        <v>122800000</v>
+      </c>
+      <c r="N49">
+        <f t="shared" si="5"/>
+        <v>152800000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A50">
+        <v>104</v>
+      </c>
+      <c r="B50">
+        <v>404</v>
+      </c>
+      <c r="C50" t="s">
+        <v>35</v>
+      </c>
+      <c r="F50" t="s">
+        <v>36</v>
+      </c>
+      <c r="G50">
+        <v>382000000</v>
+      </c>
+      <c r="H50">
+        <v>540000000</v>
+      </c>
+      <c r="I50">
+        <v>10000000</v>
+      </c>
+      <c r="J50">
+        <v>20000000</v>
+      </c>
+      <c r="K50">
+        <v>20000000</v>
+      </c>
+      <c r="L50">
+        <f t="shared" si="3"/>
+        <v>229200000</v>
+      </c>
+      <c r="M50">
+        <f t="shared" si="4"/>
+        <v>122800000</v>
+      </c>
+      <c r="N50">
+        <f t="shared" si="5"/>
+        <v>152800000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A51">
+        <v>104</v>
+      </c>
+      <c r="B51">
+        <v>501</v>
+      </c>
+      <c r="C51" t="s">
+        <v>35</v>
+      </c>
+      <c r="F51" t="s">
+        <v>36</v>
+      </c>
+      <c r="G51">
+        <v>382000000</v>
+      </c>
+      <c r="H51">
+        <v>540000000</v>
+      </c>
+      <c r="I51">
+        <v>10000000</v>
+      </c>
+      <c r="J51">
+        <v>20000000</v>
+      </c>
+      <c r="K51">
+        <v>20000000</v>
+      </c>
+      <c r="L51">
+        <f t="shared" si="3"/>
+        <v>229200000</v>
+      </c>
+      <c r="M51">
+        <f t="shared" si="4"/>
+        <v>122800000</v>
+      </c>
+      <c r="N51">
+        <f t="shared" si="5"/>
+        <v>152800000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A52">
+        <v>104</v>
+      </c>
+      <c r="B52">
+        <v>502</v>
+      </c>
+      <c r="C52" t="s">
+        <v>35</v>
+      </c>
+      <c r="F52" t="s">
+        <v>36</v>
+      </c>
+      <c r="G52">
+        <v>382000000</v>
+      </c>
+      <c r="H52">
+        <v>540000000</v>
+      </c>
+      <c r="I52">
+        <v>10000000</v>
+      </c>
+      <c r="J52">
+        <v>20000000</v>
+      </c>
+      <c r="K52">
+        <v>20000000</v>
+      </c>
+      <c r="L52">
+        <f t="shared" si="3"/>
+        <v>229200000</v>
+      </c>
+      <c r="M52">
+        <f t="shared" si="4"/>
+        <v>122800000</v>
+      </c>
+      <c r="N52">
+        <f t="shared" si="5"/>
+        <v>152800000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A53">
+        <v>104</v>
+      </c>
+      <c r="B53">
+        <v>503</v>
+      </c>
+      <c r="C53" t="s">
+        <v>35</v>
+      </c>
+      <c r="F53" t="s">
+        <v>36</v>
+      </c>
+      <c r="G53">
+        <v>382000000</v>
+      </c>
+      <c r="H53">
+        <v>540000000</v>
+      </c>
+      <c r="I53">
+        <v>10000000</v>
+      </c>
+      <c r="J53">
+        <v>20000000</v>
+      </c>
+      <c r="K53">
+        <v>20000000</v>
+      </c>
+      <c r="L53">
+        <f t="shared" si="3"/>
+        <v>229200000</v>
+      </c>
+      <c r="M53">
+        <f t="shared" si="4"/>
+        <v>122800000</v>
+      </c>
+      <c r="N53">
+        <f t="shared" si="5"/>
+        <v>152800000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A54">
+        <v>104</v>
+      </c>
+      <c r="B54">
+        <v>504</v>
+      </c>
+      <c r="C54" t="s">
+        <v>35</v>
+      </c>
+      <c r="F54" t="s">
+        <v>36</v>
+      </c>
+      <c r="G54">
+        <v>382000000</v>
+      </c>
+      <c r="H54">
+        <v>540000000</v>
+      </c>
+      <c r="I54">
+        <v>10000000</v>
+      </c>
+      <c r="J54">
+        <v>20000000</v>
+      </c>
+      <c r="K54">
+        <v>20000000</v>
+      </c>
+      <c r="L54">
+        <f t="shared" si="3"/>
+        <v>229200000</v>
+      </c>
+      <c r="M54">
+        <f t="shared" si="4"/>
+        <v>122800000</v>
+      </c>
+      <c r="N54">
+        <f t="shared" si="5"/>
+        <v>152800000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A55">
+        <v>104</v>
+      </c>
+      <c r="C55" t="s">
+        <v>37</v>
+      </c>
+      <c r="D55" t="s">
+        <v>38</v>
+      </c>
+      <c r="E55" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A56">
+        <v>104</v>
+      </c>
+      <c r="B56">
+        <v>1701</v>
+      </c>
+      <c r="C56" t="s">
+        <v>35</v>
+      </c>
+      <c r="F56" t="s">
+        <v>36</v>
+      </c>
+      <c r="G56">
+        <v>390000000</v>
+      </c>
+      <c r="H56">
+        <v>570000000</v>
+      </c>
+      <c r="I56">
+        <v>10000000</v>
+      </c>
+      <c r="J56">
+        <v>20000000</v>
+      </c>
+      <c r="K56">
+        <v>20000000</v>
+      </c>
+      <c r="L56">
+        <f t="shared" si="3"/>
+        <v>234000000</v>
+      </c>
+      <c r="M56">
+        <f t="shared" ref="M56:M115" si="6">SUM(G56-L56-I56-K56)</f>
+        <v>126000000</v>
+      </c>
+      <c r="N56">
+        <f t="shared" si="5"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A57">
+        <v>104</v>
+      </c>
+      <c r="B57">
+        <v>1702</v>
+      </c>
+      <c r="C57" t="s">
+        <v>35</v>
+      </c>
+      <c r="F57" t="s">
+        <v>36</v>
+      </c>
+      <c r="G57">
+        <v>390000000</v>
+      </c>
+      <c r="H57">
+        <v>570000000</v>
+      </c>
+      <c r="I57">
+        <v>10000000</v>
+      </c>
+      <c r="J57">
+        <v>20000000</v>
+      </c>
+      <c r="K57">
+        <v>20000000</v>
+      </c>
+      <c r="L57">
+        <f t="shared" ref="L57:L71" si="7">SUM(G57*60%)</f>
+        <v>234000000</v>
+      </c>
+      <c r="M57">
+        <f t="shared" si="6"/>
+        <v>126000000</v>
+      </c>
+      <c r="N57">
+        <f t="shared" ref="N57:N71" si="8">SUM(G57-L57)</f>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A58">
+        <v>104</v>
+      </c>
+      <c r="B58">
+        <v>1703</v>
+      </c>
+      <c r="C58" t="s">
+        <v>35</v>
+      </c>
+      <c r="F58" t="s">
+        <v>36</v>
+      </c>
+      <c r="G58">
+        <v>390000000</v>
+      </c>
+      <c r="H58">
+        <v>570000000</v>
+      </c>
+      <c r="I58">
+        <v>10000000</v>
+      </c>
+      <c r="J58">
+        <v>20000000</v>
+      </c>
+      <c r="K58">
+        <v>20000000</v>
+      </c>
+      <c r="L58">
+        <f t="shared" si="7"/>
+        <v>234000000</v>
+      </c>
+      <c r="M58">
+        <f t="shared" si="6"/>
+        <v>126000000</v>
+      </c>
+      <c r="N58">
+        <f t="shared" si="8"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A59">
+        <v>104</v>
+      </c>
+      <c r="B59">
+        <v>1704</v>
+      </c>
+      <c r="C59" t="s">
+        <v>35</v>
+      </c>
+      <c r="F59" t="s">
+        <v>36</v>
+      </c>
+      <c r="G59">
+        <v>390000000</v>
+      </c>
+      <c r="H59">
+        <v>570000000</v>
+      </c>
+      <c r="I59">
+        <v>10000000</v>
+      </c>
+      <c r="J59">
+        <v>20000000</v>
+      </c>
+      <c r="K59">
+        <v>20000000</v>
+      </c>
+      <c r="L59">
+        <f t="shared" si="7"/>
+        <v>234000000</v>
+      </c>
+      <c r="M59">
+        <f t="shared" si="6"/>
+        <v>126000000</v>
+      </c>
+      <c r="N59">
+        <f t="shared" si="8"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A60">
+        <v>104</v>
+      </c>
+      <c r="B60">
+        <v>1801</v>
+      </c>
+      <c r="C60" t="s">
+        <v>35</v>
+      </c>
+      <c r="F60" t="s">
+        <v>36</v>
+      </c>
+      <c r="G60">
+        <v>390000000</v>
+      </c>
+      <c r="H60">
+        <v>570000000</v>
+      </c>
+      <c r="I60">
+        <v>10000000</v>
+      </c>
+      <c r="J60">
+        <v>20000000</v>
+      </c>
+      <c r="K60">
+        <v>20000000</v>
+      </c>
+      <c r="L60">
+        <f t="shared" si="7"/>
+        <v>234000000</v>
+      </c>
+      <c r="M60">
+        <f t="shared" si="6"/>
+        <v>126000000</v>
+      </c>
+      <c r="N60">
+        <f t="shared" si="8"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A61">
+        <v>104</v>
+      </c>
+      <c r="B61">
+        <v>1802</v>
+      </c>
+      <c r="C61" t="s">
+        <v>35</v>
+      </c>
+      <c r="F61" t="s">
+        <v>36</v>
+      </c>
+      <c r="G61">
+        <v>390000000</v>
+      </c>
+      <c r="H61">
+        <v>570000000</v>
+      </c>
+      <c r="I61">
+        <v>10000000</v>
+      </c>
+      <c r="J61">
+        <v>20000000</v>
+      </c>
+      <c r="K61">
+        <v>20000000</v>
+      </c>
+      <c r="L61">
+        <f t="shared" si="7"/>
+        <v>234000000</v>
+      </c>
+      <c r="M61">
+        <f t="shared" si="6"/>
+        <v>126000000</v>
+      </c>
+      <c r="N61">
+        <f t="shared" si="8"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A62">
+        <v>104</v>
+      </c>
+      <c r="B62">
+        <v>1803</v>
+      </c>
+      <c r="C62" t="s">
+        <v>35</v>
+      </c>
+      <c r="F62" t="s">
+        <v>36</v>
+      </c>
+      <c r="G62">
+        <v>390000000</v>
+      </c>
+      <c r="H62">
+        <v>570000000</v>
+      </c>
+      <c r="I62">
+        <v>10000000</v>
+      </c>
+      <c r="J62">
+        <v>20000000</v>
+      </c>
+      <c r="K62">
+        <v>20000000</v>
+      </c>
+      <c r="L62">
+        <f t="shared" si="7"/>
+        <v>234000000</v>
+      </c>
+      <c r="M62">
+        <f t="shared" si="6"/>
+        <v>126000000</v>
+      </c>
+      <c r="N62">
+        <f t="shared" si="8"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A63">
+        <v>104</v>
+      </c>
+      <c r="B63">
+        <v>1804</v>
+      </c>
+      <c r="C63" t="s">
+        <v>35</v>
+      </c>
+      <c r="F63" t="s">
+        <v>36</v>
+      </c>
+      <c r="G63">
+        <v>390000000</v>
+      </c>
+      <c r="H63">
+        <v>570000000</v>
+      </c>
+      <c r="I63">
+        <v>10000000</v>
+      </c>
+      <c r="J63">
+        <v>20000000</v>
+      </c>
+      <c r="K63">
+        <v>20000000</v>
+      </c>
+      <c r="L63">
+        <f t="shared" si="7"/>
+        <v>234000000</v>
+      </c>
+      <c r="M63">
+        <f t="shared" si="6"/>
+        <v>126000000</v>
+      </c>
+      <c r="N63">
+        <f t="shared" si="8"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A64">
+        <v>104</v>
+      </c>
+      <c r="B64">
+        <v>1901</v>
+      </c>
+      <c r="C64" t="s">
+        <v>35</v>
+      </c>
+      <c r="F64" t="s">
+        <v>36</v>
+      </c>
+      <c r="G64">
+        <v>390000000</v>
+      </c>
+      <c r="H64">
+        <v>570000000</v>
+      </c>
+      <c r="I64">
+        <v>10000000</v>
+      </c>
+      <c r="J64">
+        <v>20000000</v>
+      </c>
+      <c r="K64">
+        <v>20000000</v>
+      </c>
+      <c r="L64">
+        <f t="shared" si="7"/>
+        <v>234000000</v>
+      </c>
+      <c r="M64">
+        <f t="shared" si="6"/>
+        <v>126000000</v>
+      </c>
+      <c r="N64">
+        <f t="shared" si="8"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A65">
+        <v>104</v>
+      </c>
+      <c r="B65">
+        <v>1902</v>
+      </c>
+      <c r="C65" t="s">
+        <v>35</v>
+      </c>
+      <c r="F65" t="s">
+        <v>36</v>
+      </c>
+      <c r="G65">
+        <v>390000000</v>
+      </c>
+      <c r="H65">
+        <v>570000000</v>
+      </c>
+      <c r="I65">
+        <v>10000000</v>
+      </c>
+      <c r="J65">
+        <v>20000000</v>
+      </c>
+      <c r="K65">
+        <v>20000000</v>
+      </c>
+      <c r="L65">
+        <f t="shared" si="7"/>
+        <v>234000000</v>
+      </c>
+      <c r="M65">
+        <f t="shared" si="6"/>
+        <v>126000000</v>
+      </c>
+      <c r="N65">
+        <f t="shared" si="8"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A66">
+        <v>104</v>
+      </c>
+      <c r="B66">
+        <v>1903</v>
+      </c>
+      <c r="C66" t="s">
+        <v>35</v>
+      </c>
+      <c r="F66" t="s">
+        <v>36</v>
+      </c>
+      <c r="G66">
+        <v>390000000</v>
+      </c>
+      <c r="H66">
+        <v>570000000</v>
+      </c>
+      <c r="I66">
+        <v>10000000</v>
+      </c>
+      <c r="J66">
+        <v>20000000</v>
+      </c>
+      <c r="K66">
+        <v>20000000</v>
+      </c>
+      <c r="L66">
+        <f t="shared" si="7"/>
+        <v>234000000</v>
+      </c>
+      <c r="M66">
+        <f t="shared" si="6"/>
+        <v>126000000</v>
+      </c>
+      <c r="N66">
+        <f t="shared" si="8"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A67">
+        <v>104</v>
+      </c>
+      <c r="B67">
+        <v>1904</v>
+      </c>
+      <c r="C67" t="s">
+        <v>35</v>
+      </c>
+      <c r="F67" t="s">
+        <v>36</v>
+      </c>
+      <c r="G67">
+        <v>390000000</v>
+      </c>
+      <c r="H67">
+        <v>570000000</v>
+      </c>
+      <c r="I67">
+        <v>10000000</v>
+      </c>
+      <c r="J67">
+        <v>20000000</v>
+      </c>
+      <c r="K67">
+        <v>20000000</v>
+      </c>
+      <c r="L67">
+        <f t="shared" si="7"/>
+        <v>234000000</v>
+      </c>
+      <c r="M67">
+        <f t="shared" si="6"/>
+        <v>126000000</v>
+      </c>
+      <c r="N67">
+        <f t="shared" si="8"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A68">
+        <v>104</v>
+      </c>
+      <c r="B68">
+        <v>2001</v>
+      </c>
+      <c r="C68" t="s">
+        <v>35</v>
+      </c>
+      <c r="F68" t="s">
+        <v>36</v>
+      </c>
+      <c r="G68">
+        <v>390000000</v>
+      </c>
+      <c r="H68">
+        <v>570000000</v>
+      </c>
+      <c r="I68">
+        <v>10000000</v>
+      </c>
+      <c r="J68">
+        <v>20000000</v>
+      </c>
+      <c r="K68">
+        <v>20000000</v>
+      </c>
+      <c r="L68">
+        <f t="shared" si="7"/>
+        <v>234000000</v>
+      </c>
+      <c r="M68">
+        <f t="shared" si="6"/>
+        <v>126000000</v>
+      </c>
+      <c r="N68">
+        <f t="shared" si="8"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A69">
+        <v>104</v>
+      </c>
+      <c r="B69">
+        <v>2002</v>
+      </c>
+      <c r="C69" t="s">
+        <v>35</v>
+      </c>
+      <c r="F69" t="s">
+        <v>36</v>
+      </c>
+      <c r="G69">
+        <v>390000000</v>
+      </c>
+      <c r="H69">
+        <v>570000000</v>
+      </c>
+      <c r="I69">
+        <v>10000000</v>
+      </c>
+      <c r="J69">
+        <v>20000000</v>
+      </c>
+      <c r="K69">
+        <v>20000000</v>
+      </c>
+      <c r="L69">
+        <f t="shared" si="7"/>
+        <v>234000000</v>
+      </c>
+      <c r="M69">
+        <f t="shared" si="6"/>
+        <v>126000000</v>
+      </c>
+      <c r="N69">
+        <f t="shared" si="8"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A70">
+        <v>104</v>
+      </c>
+      <c r="B70">
+        <v>2003</v>
+      </c>
+      <c r="C70" t="s">
+        <v>35</v>
+      </c>
+      <c r="F70" t="s">
+        <v>36</v>
+      </c>
+      <c r="G70">
+        <v>390000000</v>
+      </c>
+      <c r="H70">
+        <v>570000000</v>
+      </c>
+      <c r="I70">
+        <v>10000000</v>
+      </c>
+      <c r="J70">
+        <v>20000000</v>
+      </c>
+      <c r="K70">
+        <v>20000000</v>
+      </c>
+      <c r="L70">
+        <f t="shared" si="7"/>
+        <v>234000000</v>
+      </c>
+      <c r="M70">
+        <f t="shared" si="6"/>
+        <v>126000000</v>
+      </c>
+      <c r="N70">
+        <f t="shared" si="8"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A71">
+        <v>104</v>
+      </c>
+      <c r="B71">
+        <v>2004</v>
+      </c>
+      <c r="C71" t="s">
+        <v>35</v>
+      </c>
+      <c r="F71" t="s">
+        <v>36</v>
+      </c>
+      <c r="G71">
+        <v>390000000</v>
+      </c>
+      <c r="H71">
+        <v>570000000</v>
+      </c>
+      <c r="I71">
+        <v>10000000</v>
+      </c>
+      <c r="J71">
+        <v>20000000</v>
+      </c>
+      <c r="K71">
+        <v>20000000</v>
+      </c>
+      <c r="L71">
+        <f t="shared" si="7"/>
+        <v>234000000</v>
+      </c>
+      <c r="M71">
+        <f t="shared" si="6"/>
+        <v>126000000</v>
+      </c>
+      <c r="N71">
+        <f t="shared" si="8"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A72">
+        <v>104</v>
+      </c>
+      <c r="B72">
+        <v>2101</v>
+      </c>
+      <c r="C72" t="s">
+        <v>35</v>
+      </c>
+      <c r="F72" t="s">
+        <v>36</v>
+      </c>
+      <c r="G72">
+        <v>397000000</v>
+      </c>
+      <c r="H72">
+        <v>580000000</v>
+      </c>
+      <c r="I72">
+        <v>10000000</v>
+      </c>
+      <c r="J72">
+        <v>20000000</v>
+      </c>
+      <c r="K72">
+        <v>20000000</v>
+      </c>
+      <c r="L72">
+        <f t="shared" ref="L72" si="9">SUM(G72*60%)</f>
+        <v>238200000</v>
+      </c>
+      <c r="M72">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N72">
+        <f t="shared" ref="N72" si="10">SUM(G72-L72)</f>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A73">
+        <v>104</v>
+      </c>
+      <c r="B73">
+        <v>2102</v>
+      </c>
+      <c r="C73" t="s">
+        <v>35</v>
+      </c>
+      <c r="F73" t="s">
+        <v>36</v>
+      </c>
+      <c r="G73">
+        <v>397000000</v>
+      </c>
+      <c r="H73">
+        <v>580000000</v>
+      </c>
+      <c r="I73">
+        <v>10000000</v>
+      </c>
+      <c r="J73">
+        <v>20000000</v>
+      </c>
+      <c r="K73">
+        <v>20000000</v>
+      </c>
+      <c r="L73">
+        <f t="shared" ref="L73:L84" si="11">SUM(G73*60%)</f>
+        <v>238200000</v>
+      </c>
+      <c r="M73">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N73">
+        <f t="shared" ref="N73:N84" si="12">SUM(G73-L73)</f>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A74">
+        <v>104</v>
+      </c>
+      <c r="B74">
+        <v>2103</v>
+      </c>
+      <c r="C74" t="s">
+        <v>35</v>
+      </c>
+      <c r="F74" t="s">
+        <v>36</v>
+      </c>
+      <c r="G74">
+        <v>397000000</v>
+      </c>
+      <c r="H74">
+        <v>580000000</v>
+      </c>
+      <c r="I74">
+        <v>10000000</v>
+      </c>
+      <c r="J74">
+        <v>20000000</v>
+      </c>
+      <c r="K74">
+        <v>20000000</v>
+      </c>
+      <c r="L74">
+        <f t="shared" si="11"/>
+        <v>238200000</v>
+      </c>
+      <c r="M74">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N74">
+        <f t="shared" si="12"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A75">
+        <v>104</v>
+      </c>
+      <c r="B75">
+        <v>2104</v>
+      </c>
+      <c r="C75" t="s">
+        <v>35</v>
+      </c>
+      <c r="F75" t="s">
+        <v>36</v>
+      </c>
+      <c r="G75">
+        <v>397000000</v>
+      </c>
+      <c r="H75">
+        <v>580000000</v>
+      </c>
+      <c r="I75">
+        <v>10000000</v>
+      </c>
+      <c r="J75">
+        <v>20000000</v>
+      </c>
+      <c r="K75">
+        <v>20000000</v>
+      </c>
+      <c r="L75">
+        <f t="shared" si="11"/>
+        <v>238200000</v>
+      </c>
+      <c r="M75">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N75">
+        <f t="shared" si="12"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A76">
+        <v>104</v>
+      </c>
+      <c r="B76">
+        <v>2201</v>
+      </c>
+      <c r="C76" t="s">
+        <v>35</v>
+      </c>
+      <c r="F76" t="s">
+        <v>36</v>
+      </c>
+      <c r="G76">
+        <v>397000000</v>
+      </c>
+      <c r="H76">
+        <v>580000000</v>
+      </c>
+      <c r="I76">
+        <v>10000000</v>
+      </c>
+      <c r="J76">
+        <v>20000000</v>
+      </c>
+      <c r="K76">
+        <v>20000000</v>
+      </c>
+      <c r="L76">
+        <f t="shared" si="11"/>
+        <v>238200000</v>
+      </c>
+      <c r="M76">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N76">
+        <f t="shared" si="12"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A77">
+        <v>104</v>
+      </c>
+      <c r="B77">
+        <v>2202</v>
+      </c>
+      <c r="C77" t="s">
+        <v>35</v>
+      </c>
+      <c r="F77" t="s">
+        <v>36</v>
+      </c>
+      <c r="G77">
+        <v>397000000</v>
+      </c>
+      <c r="H77">
+        <v>580000000</v>
+      </c>
+      <c r="I77">
+        <v>10000000</v>
+      </c>
+      <c r="J77">
+        <v>20000000</v>
+      </c>
+      <c r="K77">
+        <v>20000000</v>
+      </c>
+      <c r="L77">
+        <f t="shared" si="11"/>
+        <v>238200000</v>
+      </c>
+      <c r="M77">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N77">
+        <f t="shared" si="12"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A78">
+        <v>104</v>
+      </c>
+      <c r="B78">
+        <v>2203</v>
+      </c>
+      <c r="C78" t="s">
+        <v>35</v>
+      </c>
+      <c r="F78" t="s">
+        <v>36</v>
+      </c>
+      <c r="G78">
+        <v>397000000</v>
+      </c>
+      <c r="H78">
+        <v>580000000</v>
+      </c>
+      <c r="I78">
+        <v>10000000</v>
+      </c>
+      <c r="J78">
+        <v>20000000</v>
+      </c>
+      <c r="K78">
+        <v>20000000</v>
+      </c>
+      <c r="L78">
+        <f t="shared" si="11"/>
+        <v>238200000</v>
+      </c>
+      <c r="M78">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N78">
+        <f t="shared" si="12"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A79">
+        <v>104</v>
+      </c>
+      <c r="B79">
+        <v>2204</v>
+      </c>
+      <c r="C79" t="s">
+        <v>35</v>
+      </c>
+      <c r="F79" t="s">
+        <v>36</v>
+      </c>
+      <c r="G79">
+        <v>397000000</v>
+      </c>
+      <c r="H79">
+        <v>580000000</v>
+      </c>
+      <c r="I79">
+        <v>10000000</v>
+      </c>
+      <c r="J79">
+        <v>20000000</v>
+      </c>
+      <c r="K79">
+        <v>20000000</v>
+      </c>
+      <c r="L79">
+        <f t="shared" si="11"/>
+        <v>238200000</v>
+      </c>
+      <c r="M79">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N79">
+        <f t="shared" si="12"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A80">
+        <v>104</v>
+      </c>
+      <c r="B80">
+        <v>2301</v>
+      </c>
+      <c r="C80" t="s">
+        <v>35</v>
+      </c>
+      <c r="F80" t="s">
+        <v>36</v>
+      </c>
+      <c r="G80">
+        <v>397000000</v>
+      </c>
+      <c r="H80">
+        <v>580000000</v>
+      </c>
+      <c r="I80">
+        <v>10000000</v>
+      </c>
+      <c r="J80">
+        <v>20000000</v>
+      </c>
+      <c r="K80">
+        <v>20000000</v>
+      </c>
+      <c r="L80">
+        <f t="shared" si="11"/>
+        <v>238200000</v>
+      </c>
+      <c r="M80">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N80">
+        <f t="shared" si="12"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A81">
+        <v>104</v>
+      </c>
+      <c r="B81">
+        <v>2302</v>
+      </c>
+      <c r="C81" t="s">
+        <v>35</v>
+      </c>
+      <c r="F81" t="s">
+        <v>36</v>
+      </c>
+      <c r="G81">
+        <v>397000000</v>
+      </c>
+      <c r="H81">
+        <v>580000000</v>
+      </c>
+      <c r="I81">
+        <v>10000000</v>
+      </c>
+      <c r="J81">
+        <v>20000000</v>
+      </c>
+      <c r="K81">
+        <v>20000000</v>
+      </c>
+      <c r="L81">
+        <f t="shared" si="11"/>
+        <v>238200000</v>
+      </c>
+      <c r="M81">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N81">
+        <f t="shared" si="12"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A82">
+        <v>104</v>
+      </c>
+      <c r="B82">
+        <v>2303</v>
+      </c>
+      <c r="C82" t="s">
+        <v>35</v>
+      </c>
+      <c r="F82" t="s">
+        <v>36</v>
+      </c>
+      <c r="G82">
+        <v>397000000</v>
+      </c>
+      <c r="H82">
+        <v>580000000</v>
+      </c>
+      <c r="I82">
+        <v>10000000</v>
+      </c>
+      <c r="J82">
+        <v>20000000</v>
+      </c>
+      <c r="K82">
+        <v>20000000</v>
+      </c>
+      <c r="L82">
+        <f t="shared" si="11"/>
+        <v>238200000</v>
+      </c>
+      <c r="M82">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N82">
+        <f t="shared" si="12"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A83">
+        <v>104</v>
+      </c>
+      <c r="B83">
+        <v>2304</v>
+      </c>
+      <c r="C83" t="s">
+        <v>35</v>
+      </c>
+      <c r="F83" t="s">
+        <v>36</v>
+      </c>
+      <c r="G83">
+        <v>397000000</v>
+      </c>
+      <c r="H83">
+        <v>580000000</v>
+      </c>
+      <c r="I83">
+        <v>10000000</v>
+      </c>
+      <c r="J83">
+        <v>20000000</v>
+      </c>
+      <c r="K83">
+        <v>20000000</v>
+      </c>
+      <c r="L83">
+        <f t="shared" si="11"/>
+        <v>238200000</v>
+      </c>
+      <c r="M83">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N83">
+        <f t="shared" si="12"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A84">
+        <v>104</v>
+      </c>
+      <c r="B84">
+        <v>2401</v>
+      </c>
+      <c r="C84" t="s">
+        <v>35</v>
+      </c>
+      <c r="F84" t="s">
+        <v>36</v>
+      </c>
+      <c r="G84">
+        <v>397000000</v>
+      </c>
+      <c r="H84">
+        <v>595000000</v>
+      </c>
+      <c r="I84">
+        <v>10000000</v>
+      </c>
+      <c r="J84">
+        <v>20000000</v>
+      </c>
+      <c r="K84">
+        <v>20000000</v>
+      </c>
+      <c r="L84">
+        <f t="shared" si="11"/>
+        <v>238200000</v>
+      </c>
+      <c r="M84">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N84">
+        <f t="shared" si="12"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A85">
+        <v>104</v>
+      </c>
+      <c r="B85">
+        <v>2402</v>
+      </c>
+      <c r="C85" t="s">
+        <v>35</v>
+      </c>
+      <c r="F85" t="s">
+        <v>36</v>
+      </c>
+      <c r="G85">
+        <v>397000000</v>
+      </c>
+      <c r="H85">
+        <v>595000000</v>
+      </c>
+      <c r="I85">
+        <v>10000000</v>
+      </c>
+      <c r="J85">
+        <v>20000000</v>
+      </c>
+      <c r="K85">
+        <v>20000000</v>
+      </c>
+      <c r="L85">
+        <f t="shared" ref="L85:L96" si="13">SUM(G85*60%)</f>
+        <v>238200000</v>
+      </c>
+      <c r="M85">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N85">
+        <f t="shared" ref="N85:N96" si="14">SUM(G85-L85)</f>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A86">
+        <v>104</v>
+      </c>
+      <c r="B86">
+        <v>2403</v>
+      </c>
+      <c r="C86" t="s">
+        <v>35</v>
+      </c>
+      <c r="F86" t="s">
+        <v>36</v>
+      </c>
+      <c r="G86">
+        <v>397000000</v>
+      </c>
+      <c r="H86">
+        <v>595000000</v>
+      </c>
+      <c r="I86">
+        <v>10000000</v>
+      </c>
+      <c r="J86">
+        <v>20000000</v>
+      </c>
+      <c r="K86">
+        <v>20000000</v>
+      </c>
+      <c r="L86">
+        <f t="shared" si="13"/>
+        <v>238200000</v>
+      </c>
+      <c r="M86">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N86">
+        <f t="shared" si="14"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A87">
+        <v>104</v>
+      </c>
+      <c r="B87">
+        <v>2404</v>
+      </c>
+      <c r="C87" t="s">
+        <v>35</v>
+      </c>
+      <c r="F87" t="s">
+        <v>36</v>
+      </c>
+      <c r="G87">
+        <v>397000000</v>
+      </c>
+      <c r="H87">
+        <v>595000000</v>
+      </c>
+      <c r="I87">
+        <v>10000000</v>
+      </c>
+      <c r="J87">
+        <v>20000000</v>
+      </c>
+      <c r="K87">
+        <v>20000000</v>
+      </c>
+      <c r="L87">
+        <f t="shared" si="13"/>
+        <v>238200000</v>
+      </c>
+      <c r="M87">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N87">
+        <f t="shared" si="14"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A88">
+        <v>104</v>
+      </c>
+      <c r="B88">
+        <v>2501</v>
+      </c>
+      <c r="C88" t="s">
+        <v>35</v>
+      </c>
+      <c r="F88" t="s">
+        <v>36</v>
+      </c>
+      <c r="G88">
+        <v>397000000</v>
+      </c>
+      <c r="H88">
+        <v>595000000</v>
+      </c>
+      <c r="I88">
+        <v>10000000</v>
+      </c>
+      <c r="J88">
+        <v>20000000</v>
+      </c>
+      <c r="K88">
+        <v>20000000</v>
+      </c>
+      <c r="L88">
+        <f t="shared" si="13"/>
+        <v>238200000</v>
+      </c>
+      <c r="M88">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N88">
+        <f t="shared" si="14"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A89">
+        <v>104</v>
+      </c>
+      <c r="B89">
+        <v>2502</v>
+      </c>
+      <c r="C89" t="s">
+        <v>35</v>
+      </c>
+      <c r="F89" t="s">
+        <v>36</v>
+      </c>
+      <c r="G89">
+        <v>397000000</v>
+      </c>
+      <c r="H89">
+        <v>595000000</v>
+      </c>
+      <c r="I89">
+        <v>10000000</v>
+      </c>
+      <c r="J89">
+        <v>20000000</v>
+      </c>
+      <c r="K89">
+        <v>20000000</v>
+      </c>
+      <c r="L89">
+        <f t="shared" si="13"/>
+        <v>238200000</v>
+      </c>
+      <c r="M89">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N89">
+        <f t="shared" si="14"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A90">
+        <v>104</v>
+      </c>
+      <c r="B90">
+        <v>2503</v>
+      </c>
+      <c r="C90" t="s">
+        <v>35</v>
+      </c>
+      <c r="F90" t="s">
+        <v>36</v>
+      </c>
+      <c r="G90">
+        <v>397000000</v>
+      </c>
+      <c r="H90">
+        <v>595000000</v>
+      </c>
+      <c r="I90">
+        <v>10000000</v>
+      </c>
+      <c r="J90">
+        <v>20000000</v>
+      </c>
+      <c r="K90">
+        <v>20000000</v>
+      </c>
+      <c r="L90">
+        <f t="shared" si="13"/>
+        <v>238200000</v>
+      </c>
+      <c r="M90">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N90">
+        <f t="shared" si="14"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A91">
+        <v>104</v>
+      </c>
+      <c r="B91">
+        <v>2504</v>
+      </c>
+      <c r="C91" t="s">
+        <v>35</v>
+      </c>
+      <c r="F91" t="s">
+        <v>36</v>
+      </c>
+      <c r="G91">
+        <v>397000000</v>
+      </c>
+      <c r="H91">
+        <v>595000000</v>
+      </c>
+      <c r="I91">
+        <v>10000000</v>
+      </c>
+      <c r="J91">
+        <v>20000000</v>
+      </c>
+      <c r="K91">
+        <v>20000000</v>
+      </c>
+      <c r="L91">
+        <f t="shared" si="13"/>
+        <v>238200000</v>
+      </c>
+      <c r="M91">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N91">
+        <f t="shared" si="14"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A92">
+        <v>104</v>
+      </c>
+      <c r="B92">
+        <v>2601</v>
+      </c>
+      <c r="C92" t="s">
+        <v>35</v>
+      </c>
+      <c r="F92" t="s">
+        <v>36</v>
+      </c>
+      <c r="G92">
+        <v>397000000</v>
+      </c>
+      <c r="H92">
+        <v>595000000</v>
+      </c>
+      <c r="I92">
+        <v>10000000</v>
+      </c>
+      <c r="J92">
+        <v>20000000</v>
+      </c>
+      <c r="K92">
+        <v>20000000</v>
+      </c>
+      <c r="L92">
+        <f t="shared" si="13"/>
+        <v>238200000</v>
+      </c>
+      <c r="M92">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N92">
+        <f t="shared" si="14"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A93">
+        <v>104</v>
+      </c>
+      <c r="B93">
+        <v>2602</v>
+      </c>
+      <c r="C93" t="s">
+        <v>35</v>
+      </c>
+      <c r="F93" t="s">
+        <v>36</v>
+      </c>
+      <c r="G93">
+        <v>397000000</v>
+      </c>
+      <c r="H93">
+        <v>595000000</v>
+      </c>
+      <c r="I93">
+        <v>10000000</v>
+      </c>
+      <c r="J93">
+        <v>20000000</v>
+      </c>
+      <c r="K93">
+        <v>20000000</v>
+      </c>
+      <c r="L93">
+        <f t="shared" si="13"/>
+        <v>238200000</v>
+      </c>
+      <c r="M93">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N93">
+        <f t="shared" si="14"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A94">
+        <v>104</v>
+      </c>
+      <c r="B94">
+        <v>2603</v>
+      </c>
+      <c r="C94" t="s">
+        <v>35</v>
+      </c>
+      <c r="F94" t="s">
+        <v>36</v>
+      </c>
+      <c r="G94">
+        <v>397000000</v>
+      </c>
+      <c r="H94">
+        <v>595000000</v>
+      </c>
+      <c r="I94">
+        <v>10000000</v>
+      </c>
+      <c r="J94">
+        <v>20000000</v>
+      </c>
+      <c r="K94">
+        <v>20000000</v>
+      </c>
+      <c r="L94">
+        <f t="shared" si="13"/>
+        <v>238200000</v>
+      </c>
+      <c r="M94">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N94">
+        <f t="shared" si="14"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A95">
+        <v>104</v>
+      </c>
+      <c r="B95">
+        <v>2604</v>
+      </c>
+      <c r="C95" t="s">
+        <v>35</v>
+      </c>
+      <c r="F95" t="s">
+        <v>36</v>
+      </c>
+      <c r="G95">
+        <v>397000000</v>
+      </c>
+      <c r="H95">
+        <v>595000000</v>
+      </c>
+      <c r="I95">
+        <v>10000000</v>
+      </c>
+      <c r="J95">
+        <v>20000000</v>
+      </c>
+      <c r="K95">
+        <v>20000000</v>
+      </c>
+      <c r="L95">
+        <f t="shared" si="13"/>
+        <v>238200000</v>
+      </c>
+      <c r="M95">
+        <f t="shared" si="6"/>
+        <v>128800000</v>
+      </c>
+      <c r="N95">
+        <f t="shared" si="14"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A96">
+        <v>105</v>
+      </c>
+      <c r="B96">
+        <v>101</v>
+      </c>
+      <c r="C96" t="s">
+        <v>35</v>
+      </c>
+      <c r="F96" t="s">
+        <v>36</v>
+      </c>
+      <c r="G96">
+        <v>363000000</v>
+      </c>
+      <c r="H96">
+        <v>525000000</v>
+      </c>
+      <c r="I96">
+        <v>10000000</v>
+      </c>
+      <c r="J96">
+        <v>20000000</v>
+      </c>
+      <c r="K96">
+        <v>20000000</v>
+      </c>
+      <c r="L96">
+        <f t="shared" si="13"/>
+        <v>217800000</v>
+      </c>
+      <c r="M96">
+        <f t="shared" si="6"/>
+        <v>115200000</v>
+      </c>
+      <c r="N96">
+        <f t="shared" si="14"/>
+        <v>145200000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A97">
+        <v>105</v>
+      </c>
+      <c r="B97">
+        <v>102</v>
+      </c>
+      <c r="C97" t="s">
+        <v>35</v>
+      </c>
+      <c r="F97" t="s">
+        <v>36</v>
+      </c>
+      <c r="G97">
+        <v>363000000</v>
+      </c>
+      <c r="H97">
+        <v>525000000</v>
+      </c>
+      <c r="I97">
+        <v>10000000</v>
+      </c>
+      <c r="J97">
+        <v>20000000</v>
+      </c>
+      <c r="K97">
+        <v>20000000</v>
+      </c>
+      <c r="L97">
+        <f t="shared" ref="L97:L100" si="15">SUM(G97*60%)</f>
+        <v>217800000</v>
+      </c>
+      <c r="M97">
+        <f t="shared" si="6"/>
+        <v>115200000</v>
+      </c>
+      <c r="N97">
+        <f t="shared" ref="N97:N100" si="16">SUM(G97-L97)</f>
+        <v>145200000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A98">
+        <v>105</v>
+      </c>
+      <c r="B98">
+        <v>103</v>
+      </c>
+      <c r="C98" t="s">
+        <v>35</v>
+      </c>
+      <c r="F98" t="s">
+        <v>36</v>
+      </c>
+      <c r="G98">
+        <v>363000000</v>
+      </c>
+      <c r="H98">
+        <v>525000000</v>
+      </c>
+      <c r="I98">
+        <v>10000000</v>
+      </c>
+      <c r="J98">
+        <v>20000000</v>
+      </c>
+      <c r="K98">
+        <v>20000000</v>
+      </c>
+      <c r="L98">
+        <f t="shared" si="15"/>
+        <v>217800000</v>
+      </c>
+      <c r="M98">
+        <f t="shared" si="6"/>
+        <v>115200000</v>
+      </c>
+      <c r="N98">
+        <f t="shared" si="16"/>
+        <v>145200000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A99">
+        <v>105</v>
+      </c>
+      <c r="B99">
+        <v>104</v>
+      </c>
+      <c r="C99" t="s">
+        <v>35</v>
+      </c>
+      <c r="F99" t="s">
+        <v>36</v>
+      </c>
+      <c r="G99">
+        <v>363000000</v>
+      </c>
+      <c r="H99">
+        <v>525000000</v>
+      </c>
+      <c r="I99">
+        <v>10000000</v>
+      </c>
+      <c r="J99">
+        <v>20000000</v>
+      </c>
+      <c r="K99">
+        <v>20000000</v>
+      </c>
+      <c r="L99">
+        <f t="shared" si="15"/>
+        <v>217800000</v>
+      </c>
+      <c r="M99">
+        <f t="shared" si="6"/>
+        <v>115200000</v>
+      </c>
+      <c r="N99">
+        <f t="shared" si="16"/>
+        <v>145200000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A100">
+        <v>105</v>
+      </c>
+      <c r="B100">
+        <v>201</v>
+      </c>
+      <c r="C100" t="s">
+        <v>35</v>
+      </c>
+      <c r="F100" t="s">
+        <v>36</v>
+      </c>
+      <c r="G100">
+        <v>374000000</v>
+      </c>
+      <c r="H100">
+        <v>530000000</v>
+      </c>
+      <c r="I100">
+        <v>10000000</v>
+      </c>
+      <c r="J100">
+        <v>20000000</v>
+      </c>
+      <c r="K100">
+        <v>20000000</v>
+      </c>
+      <c r="L100">
+        <f t="shared" si="15"/>
+        <v>224400000</v>
+      </c>
+      <c r="M100">
+        <f t="shared" si="6"/>
+        <v>119600000</v>
+      </c>
+      <c r="N100">
+        <f t="shared" si="16"/>
+        <v>149600000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A101">
+        <v>105</v>
+      </c>
+      <c r="B101">
+        <v>202</v>
+      </c>
+      <c r="C101" t="s">
+        <v>35</v>
+      </c>
+      <c r="F101" t="s">
+        <v>36</v>
+      </c>
+      <c r="G101">
+        <v>374000000</v>
+      </c>
+      <c r="H101">
+        <v>530000000</v>
+      </c>
+      <c r="I101">
+        <v>10000000</v>
+      </c>
+      <c r="J101">
+        <v>20000000</v>
+      </c>
+      <c r="K101">
+        <v>20000000</v>
+      </c>
+      <c r="L101">
+        <f t="shared" ref="L101:L104" si="17">SUM(G101*60%)</f>
+        <v>224400000</v>
+      </c>
+      <c r="M101">
+        <f t="shared" si="6"/>
+        <v>119600000</v>
+      </c>
+      <c r="N101">
+        <f t="shared" ref="N101:N104" si="18">SUM(G101-L101)</f>
+        <v>149600000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A102">
+        <v>105</v>
+      </c>
+      <c r="B102">
+        <v>203</v>
+      </c>
+      <c r="C102" t="s">
+        <v>35</v>
+      </c>
+      <c r="F102" t="s">
+        <v>36</v>
+      </c>
+      <c r="G102">
+        <v>374000000</v>
+      </c>
+      <c r="H102">
+        <v>530000000</v>
+      </c>
+      <c r="I102">
+        <v>10000000</v>
+      </c>
+      <c r="J102">
+        <v>20000000</v>
+      </c>
+      <c r="K102">
+        <v>20000000</v>
+      </c>
+      <c r="L102">
+        <f t="shared" si="17"/>
+        <v>224400000</v>
+      </c>
+      <c r="M102">
+        <f t="shared" si="6"/>
+        <v>119600000</v>
+      </c>
+      <c r="N102">
+        <f t="shared" si="18"/>
+        <v>149600000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A103">
+        <v>105</v>
+      </c>
+      <c r="B103">
+        <v>204</v>
+      </c>
+      <c r="C103" t="s">
+        <v>35</v>
+      </c>
+      <c r="F103" t="s">
+        <v>36</v>
+      </c>
+      <c r="G103">
+        <v>374000000</v>
+      </c>
+      <c r="H103">
+        <v>530000000</v>
+      </c>
+      <c r="I103">
+        <v>10000000</v>
+      </c>
+      <c r="J103">
+        <v>20000000</v>
+      </c>
+      <c r="K103">
+        <v>20000000</v>
+      </c>
+      <c r="L103">
+        <f t="shared" si="17"/>
+        <v>224400000</v>
+      </c>
+      <c r="M103">
+        <f t="shared" si="6"/>
+        <v>119600000</v>
+      </c>
+      <c r="N103">
+        <f t="shared" si="18"/>
+        <v>149600000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A104">
+        <v>105</v>
+      </c>
+      <c r="B104">
+        <v>301</v>
+      </c>
+      <c r="C104" t="s">
+        <v>35</v>
+      </c>
+      <c r="F104" t="s">
+        <v>36</v>
+      </c>
+      <c r="G104">
+        <v>374000000</v>
+      </c>
+      <c r="H104">
+        <v>535000000</v>
+      </c>
+      <c r="I104">
+        <v>10000000</v>
+      </c>
+      <c r="J104">
+        <v>20000000</v>
+      </c>
+      <c r="K104">
+        <v>20000000</v>
+      </c>
+      <c r="L104">
+        <f t="shared" si="17"/>
+        <v>224400000</v>
+      </c>
+      <c r="M104">
+        <f t="shared" si="6"/>
+        <v>119600000</v>
+      </c>
+      <c r="N104">
+        <f t="shared" si="18"/>
+        <v>149600000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A105">
+        <v>105</v>
+      </c>
+      <c r="B105">
+        <v>302</v>
+      </c>
+      <c r="C105" t="s">
+        <v>35</v>
+      </c>
+      <c r="F105" t="s">
+        <v>36</v>
+      </c>
+      <c r="G105">
+        <v>374000000</v>
+      </c>
+      <c r="H105">
+        <v>535000000</v>
+      </c>
+      <c r="I105">
+        <v>10000000</v>
+      </c>
+      <c r="J105">
+        <v>20000000</v>
+      </c>
+      <c r="K105">
+        <v>20000000</v>
+      </c>
+      <c r="L105">
+        <f t="shared" ref="L105:L109" si="19">SUM(G105*60%)</f>
+        <v>224400000</v>
+      </c>
+      <c r="M105">
+        <f t="shared" si="6"/>
+        <v>119600000</v>
+      </c>
+      <c r="N105">
+        <f t="shared" ref="N105:N109" si="20">SUM(G105-L105)</f>
+        <v>149600000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>303</v>
+      </c>
+      <c r="C106" t="s">
+        <v>35</v>
+      </c>
+      <c r="F106" t="s">
+        <v>36</v>
+      </c>
+      <c r="G106">
+        <v>374000000</v>
+      </c>
+      <c r="H106">
+        <v>535000000</v>
+      </c>
+      <c r="I106">
+        <v>10000000</v>
+      </c>
+      <c r="J106">
+        <v>20000000</v>
+      </c>
+      <c r="K106">
+        <v>20000000</v>
+      </c>
+      <c r="L106">
+        <f t="shared" si="19"/>
+        <v>224400000</v>
+      </c>
+      <c r="M106">
+        <f t="shared" si="6"/>
+        <v>119600000</v>
+      </c>
+      <c r="N106">
+        <f t="shared" si="20"/>
+        <v>149600000</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A107">
+        <v>105</v>
+      </c>
+      <c r="B107">
+        <v>304</v>
+      </c>
+      <c r="C107" t="s">
+        <v>35</v>
+      </c>
+      <c r="F107" t="s">
+        <v>36</v>
+      </c>
+      <c r="G107">
+        <v>374000000</v>
+      </c>
+      <c r="H107">
+        <v>535000000</v>
+      </c>
+      <c r="I107">
+        <v>10000000</v>
+      </c>
+      <c r="J107">
+        <v>20000000</v>
+      </c>
+      <c r="K107">
+        <v>20000000</v>
+      </c>
+      <c r="L107">
+        <f t="shared" si="19"/>
+        <v>224400000</v>
+      </c>
+      <c r="M107">
+        <f t="shared" si="6"/>
+        <v>119600000</v>
+      </c>
+      <c r="N107">
+        <f t="shared" si="20"/>
+        <v>149600000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A108">
+        <v>105</v>
+      </c>
+      <c r="B108">
+        <v>401</v>
+      </c>
+      <c r="C108" t="s">
+        <v>35</v>
+      </c>
+      <c r="F108" t="s">
+        <v>36</v>
+      </c>
+      <c r="G108">
+        <v>382000000</v>
+      </c>
+      <c r="H108">
+        <v>540000000</v>
+      </c>
+      <c r="I108">
+        <v>10000000</v>
+      </c>
+      <c r="J108">
+        <v>20000000</v>
+      </c>
+      <c r="K108">
+        <v>20000000</v>
+      </c>
+      <c r="L108">
+        <f t="shared" si="19"/>
+        <v>229200000</v>
+      </c>
+      <c r="M108">
+        <f t="shared" si="6"/>
+        <v>122800000</v>
+      </c>
+      <c r="N108">
+        <f t="shared" si="20"/>
+        <v>152800000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A109">
+        <v>105</v>
+      </c>
+      <c r="B109">
+        <v>402</v>
+      </c>
+      <c r="C109" t="s">
+        <v>35</v>
+      </c>
+      <c r="F109" t="s">
+        <v>36</v>
+      </c>
+      <c r="G109">
+        <v>382000000</v>
+      </c>
+      <c r="H109">
+        <v>540000000</v>
+      </c>
+      <c r="I109">
+        <v>10000000</v>
+      </c>
+      <c r="J109">
+        <v>20000000</v>
+      </c>
+      <c r="K109">
+        <v>20000000</v>
+      </c>
+      <c r="L109">
+        <f t="shared" si="19"/>
+        <v>229200000</v>
+      </c>
+      <c r="M109">
+        <f t="shared" si="6"/>
+        <v>122800000</v>
+      </c>
+      <c r="N109">
+        <f t="shared" si="20"/>
+        <v>152800000</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A110">
+        <v>105</v>
+      </c>
+      <c r="B110">
+        <v>403</v>
+      </c>
+      <c r="C110" t="s">
+        <v>35</v>
+      </c>
+      <c r="F110" t="s">
+        <v>36</v>
+      </c>
+      <c r="G110">
+        <v>382000000</v>
+      </c>
+      <c r="H110">
+        <v>540000000</v>
+      </c>
+      <c r="I110">
+        <v>10000000</v>
+      </c>
+      <c r="J110">
+        <v>20000000</v>
+      </c>
+      <c r="K110">
+        <v>20000000</v>
+      </c>
+      <c r="L110">
+        <f t="shared" ref="L110:L117" si="21">SUM(G110*60%)</f>
+        <v>229200000</v>
+      </c>
+      <c r="M110">
+        <f t="shared" si="6"/>
+        <v>122800000</v>
+      </c>
+      <c r="N110">
+        <f t="shared" ref="N110:N117" si="22">SUM(G110-L110)</f>
+        <v>152800000</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A111">
+        <v>105</v>
+      </c>
+      <c r="B111">
+        <v>404</v>
+      </c>
+      <c r="C111" t="s">
+        <v>35</v>
+      </c>
+      <c r="F111" t="s">
+        <v>36</v>
+      </c>
+      <c r="G111">
+        <v>382000000</v>
+      </c>
+      <c r="H111">
+        <v>540000000</v>
+      </c>
+      <c r="I111">
+        <v>10000000</v>
+      </c>
+      <c r="J111">
+        <v>20000000</v>
+      </c>
+      <c r="K111">
+        <v>20000000</v>
+      </c>
+      <c r="L111">
+        <f t="shared" si="21"/>
+        <v>229200000</v>
+      </c>
+      <c r="M111">
+        <f t="shared" si="6"/>
+        <v>122800000</v>
+      </c>
+      <c r="N111">
+        <f t="shared" si="22"/>
+        <v>152800000</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A112">
+        <v>105</v>
+      </c>
+      <c r="B112">
+        <v>501</v>
+      </c>
+      <c r="C112" t="s">
+        <v>35</v>
+      </c>
+      <c r="F112" t="s">
+        <v>36</v>
+      </c>
+      <c r="G112">
+        <v>382000000</v>
+      </c>
+      <c r="H112">
+        <v>540000000</v>
+      </c>
+      <c r="I112">
+        <v>10000000</v>
+      </c>
+      <c r="J112">
+        <v>20000000</v>
+      </c>
+      <c r="K112">
+        <v>20000000</v>
+      </c>
+      <c r="L112">
+        <f t="shared" si="21"/>
+        <v>229200000</v>
+      </c>
+      <c r="M112">
+        <f t="shared" si="6"/>
+        <v>122800000</v>
+      </c>
+      <c r="N112">
+        <f t="shared" si="22"/>
+        <v>152800000</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A113">
+        <v>105</v>
+      </c>
+      <c r="B113">
+        <v>502</v>
+      </c>
+      <c r="C113" t="s">
+        <v>35</v>
+      </c>
+      <c r="F113" t="s">
+        <v>36</v>
+      </c>
+      <c r="G113">
+        <v>382000000</v>
+      </c>
+      <c r="H113">
+        <v>540000000</v>
+      </c>
+      <c r="I113">
+        <v>10000000</v>
+      </c>
+      <c r="J113">
+        <v>20000000</v>
+      </c>
+      <c r="K113">
+        <v>20000000</v>
+      </c>
+      <c r="L113">
+        <f t="shared" si="21"/>
+        <v>229200000</v>
+      </c>
+      <c r="M113">
+        <f t="shared" si="6"/>
+        <v>122800000</v>
+      </c>
+      <c r="N113">
+        <f t="shared" si="22"/>
+        <v>152800000</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A114">
+        <v>105</v>
+      </c>
+      <c r="B114">
+        <v>503</v>
+      </c>
+      <c r="C114" t="s">
+        <v>35</v>
+      </c>
+      <c r="F114" t="s">
+        <v>36</v>
+      </c>
+      <c r="G114">
+        <v>382000000</v>
+      </c>
+      <c r="H114">
+        <v>540000000</v>
+      </c>
+      <c r="I114">
+        <v>10000000</v>
+      </c>
+      <c r="J114">
+        <v>20000000</v>
+      </c>
+      <c r="K114">
+        <v>20000000</v>
+      </c>
+      <c r="L114">
+        <f t="shared" si="21"/>
+        <v>229200000</v>
+      </c>
+      <c r="M114">
+        <f t="shared" si="6"/>
+        <v>122800000</v>
+      </c>
+      <c r="N114">
+        <f t="shared" si="22"/>
+        <v>152800000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A115">
+        <v>105</v>
+      </c>
+      <c r="B115">
+        <v>504</v>
+      </c>
+      <c r="C115" t="s">
+        <v>35</v>
+      </c>
+      <c r="F115" t="s">
+        <v>36</v>
+      </c>
+      <c r="G115">
+        <v>382000000</v>
+      </c>
+      <c r="H115">
+        <v>540000000</v>
+      </c>
+      <c r="I115">
+        <v>10000000</v>
+      </c>
+      <c r="J115">
+        <v>20000000</v>
+      </c>
+      <c r="K115">
+        <v>20000000</v>
+      </c>
+      <c r="L115">
+        <f t="shared" si="21"/>
+        <v>229200000</v>
+      </c>
+      <c r="M115">
+        <f t="shared" si="6"/>
+        <v>122800000</v>
+      </c>
+      <c r="N115">
+        <f t="shared" si="22"/>
+        <v>152800000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A116">
+        <v>105</v>
+      </c>
+      <c r="C116" t="s">
+        <v>37</v>
+      </c>
+      <c r="D116" t="s">
+        <v>14</v>
+      </c>
+      <c r="E116" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A117">
+        <v>105</v>
+      </c>
+      <c r="B117">
+        <v>1701</v>
+      </c>
+      <c r="C117" t="s">
+        <v>35</v>
+      </c>
+      <c r="F117" t="s">
+        <v>36</v>
+      </c>
+      <c r="G117">
+        <v>390000000</v>
+      </c>
+      <c r="H117">
+        <v>570000000</v>
+      </c>
+      <c r="I117">
+        <v>10000000</v>
+      </c>
+      <c r="J117">
+        <v>20000000</v>
+      </c>
+      <c r="K117">
+        <v>20000000</v>
+      </c>
+      <c r="L117">
+        <f t="shared" si="21"/>
+        <v>234000000</v>
+      </c>
+      <c r="M117">
+        <f t="shared" ref="M117:M148" si="23">SUM(G117-L117-I117-K117)</f>
+        <v>126000000</v>
+      </c>
+      <c r="N117">
+        <f t="shared" si="22"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A118">
+        <v>105</v>
+      </c>
+      <c r="B118">
+        <v>1702</v>
+      </c>
+      <c r="C118" t="s">
+        <v>35</v>
+      </c>
+      <c r="F118" t="s">
+        <v>36</v>
+      </c>
+      <c r="G118">
+        <v>390000000</v>
+      </c>
+      <c r="H118">
+        <v>570000000</v>
+      </c>
+      <c r="I118">
+        <v>10000000</v>
+      </c>
+      <c r="J118">
+        <v>20000000</v>
+      </c>
+      <c r="K118">
+        <v>20000000</v>
+      </c>
+      <c r="L118">
+        <f t="shared" ref="L118:L133" si="24">SUM(G118*60%)</f>
+        <v>234000000</v>
+      </c>
+      <c r="M118">
+        <f t="shared" si="23"/>
+        <v>126000000</v>
+      </c>
+      <c r="N118">
+        <f t="shared" ref="N118:N133" si="25">SUM(G118-L118)</f>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A119">
+        <v>105</v>
+      </c>
+      <c r="B119">
+        <v>1703</v>
+      </c>
+      <c r="C119" t="s">
+        <v>35</v>
+      </c>
+      <c r="F119" t="s">
+        <v>36</v>
+      </c>
+      <c r="G119">
+        <v>390000000</v>
+      </c>
+      <c r="H119">
+        <v>570000000</v>
+      </c>
+      <c r="I119">
+        <v>10000000</v>
+      </c>
+      <c r="J119">
+        <v>20000000</v>
+      </c>
+      <c r="K119">
+        <v>20000000</v>
+      </c>
+      <c r="L119">
+        <f t="shared" si="24"/>
+        <v>234000000</v>
+      </c>
+      <c r="M119">
+        <f t="shared" si="23"/>
+        <v>126000000</v>
+      </c>
+      <c r="N119">
+        <f t="shared" si="25"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A120">
+        <v>105</v>
+      </c>
+      <c r="B120">
+        <v>1704</v>
+      </c>
+      <c r="C120" t="s">
+        <v>35</v>
+      </c>
+      <c r="F120" t="s">
+        <v>36</v>
+      </c>
+      <c r="G120">
+        <v>390000000</v>
+      </c>
+      <c r="H120">
+        <v>570000000</v>
+      </c>
+      <c r="I120">
+        <v>10000000</v>
+      </c>
+      <c r="J120">
+        <v>20000000</v>
+      </c>
+      <c r="K120">
+        <v>20000000</v>
+      </c>
+      <c r="L120">
+        <f t="shared" si="24"/>
+        <v>234000000</v>
+      </c>
+      <c r="M120">
+        <f t="shared" si="23"/>
+        <v>126000000</v>
+      </c>
+      <c r="N120">
+        <f t="shared" si="25"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A121">
+        <v>105</v>
+      </c>
+      <c r="B121">
+        <v>1801</v>
+      </c>
+      <c r="C121" t="s">
+        <v>35</v>
+      </c>
+      <c r="F121" t="s">
+        <v>36</v>
+      </c>
+      <c r="G121">
+        <v>390000000</v>
+      </c>
+      <c r="H121">
+        <v>570000000</v>
+      </c>
+      <c r="I121">
+        <v>10000000</v>
+      </c>
+      <c r="J121">
+        <v>20000000</v>
+      </c>
+      <c r="K121">
+        <v>20000000</v>
+      </c>
+      <c r="L121">
+        <f t="shared" si="24"/>
+        <v>234000000</v>
+      </c>
+      <c r="M121">
+        <f t="shared" si="23"/>
+        <v>126000000</v>
+      </c>
+      <c r="N121">
+        <f t="shared" si="25"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A122">
+        <v>105</v>
+      </c>
+      <c r="B122">
+        <v>1802</v>
+      </c>
+      <c r="C122" t="s">
+        <v>35</v>
+      </c>
+      <c r="F122" t="s">
+        <v>36</v>
+      </c>
+      <c r="G122">
+        <v>390000000</v>
+      </c>
+      <c r="H122">
+        <v>570000000</v>
+      </c>
+      <c r="I122">
+        <v>10000000</v>
+      </c>
+      <c r="J122">
+        <v>20000000</v>
+      </c>
+      <c r="K122">
+        <v>20000000</v>
+      </c>
+      <c r="L122">
+        <f t="shared" si="24"/>
+        <v>234000000</v>
+      </c>
+      <c r="M122">
+        <f t="shared" si="23"/>
+        <v>126000000</v>
+      </c>
+      <c r="N122">
+        <f t="shared" si="25"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A123">
+        <v>105</v>
+      </c>
+      <c r="B123">
+        <v>1803</v>
+      </c>
+      <c r="C123" t="s">
+        <v>35</v>
+      </c>
+      <c r="F123" t="s">
+        <v>36</v>
+      </c>
+      <c r="G123">
+        <v>390000000</v>
+      </c>
+      <c r="H123">
+        <v>570000000</v>
+      </c>
+      <c r="I123">
+        <v>10000000</v>
+      </c>
+      <c r="J123">
+        <v>20000000</v>
+      </c>
+      <c r="K123">
+        <v>20000000</v>
+      </c>
+      <c r="L123">
+        <f t="shared" si="24"/>
+        <v>234000000</v>
+      </c>
+      <c r="M123">
+        <f t="shared" si="23"/>
+        <v>126000000</v>
+      </c>
+      <c r="N123">
+        <f t="shared" si="25"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A124">
+        <v>105</v>
+      </c>
+      <c r="B124">
+        <v>1804</v>
+      </c>
+      <c r="C124" t="s">
+        <v>35</v>
+      </c>
+      <c r="F124" t="s">
+        <v>36</v>
+      </c>
+      <c r="G124">
+        <v>390000000</v>
+      </c>
+      <c r="H124">
+        <v>570000000</v>
+      </c>
+      <c r="I124">
+        <v>10000000</v>
+      </c>
+      <c r="J124">
+        <v>20000000</v>
+      </c>
+      <c r="K124">
+        <v>20000000</v>
+      </c>
+      <c r="L124">
+        <f t="shared" si="24"/>
+        <v>234000000</v>
+      </c>
+      <c r="M124">
+        <f t="shared" si="23"/>
+        <v>126000000</v>
+      </c>
+      <c r="N124">
+        <f t="shared" si="25"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A125">
+        <v>105</v>
+      </c>
+      <c r="B125">
+        <v>1901</v>
+      </c>
+      <c r="C125" t="s">
+        <v>35</v>
+      </c>
+      <c r="F125" t="s">
+        <v>36</v>
+      </c>
+      <c r="G125">
+        <v>390000000</v>
+      </c>
+      <c r="H125">
+        <v>570000000</v>
+      </c>
+      <c r="I125">
+        <v>10000000</v>
+      </c>
+      <c r="J125">
+        <v>20000000</v>
+      </c>
+      <c r="K125">
+        <v>20000000</v>
+      </c>
+      <c r="L125">
+        <f t="shared" si="24"/>
+        <v>234000000</v>
+      </c>
+      <c r="M125">
+        <f t="shared" si="23"/>
+        <v>126000000</v>
+      </c>
+      <c r="N125">
+        <f t="shared" si="25"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A126">
+        <v>105</v>
+      </c>
+      <c r="B126">
+        <v>1902</v>
+      </c>
+      <c r="C126" t="s">
+        <v>35</v>
+      </c>
+      <c r="F126" t="s">
+        <v>36</v>
+      </c>
+      <c r="G126">
+        <v>390000000</v>
+      </c>
+      <c r="H126">
+        <v>570000000</v>
+      </c>
+      <c r="I126">
+        <v>10000000</v>
+      </c>
+      <c r="J126">
+        <v>20000000</v>
+      </c>
+      <c r="K126">
+        <v>20000000</v>
+      </c>
+      <c r="L126">
+        <f t="shared" si="24"/>
+        <v>234000000</v>
+      </c>
+      <c r="M126">
+        <f t="shared" si="23"/>
+        <v>126000000</v>
+      </c>
+      <c r="N126">
+        <f t="shared" si="25"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A127">
+        <v>105</v>
+      </c>
+      <c r="B127">
+        <v>1903</v>
+      </c>
+      <c r="C127" t="s">
+        <v>35</v>
+      </c>
+      <c r="F127" t="s">
+        <v>36</v>
+      </c>
+      <c r="G127">
+        <v>390000000</v>
+      </c>
+      <c r="H127">
+        <v>570000000</v>
+      </c>
+      <c r="I127">
+        <v>10000000</v>
+      </c>
+      <c r="J127">
+        <v>20000000</v>
+      </c>
+      <c r="K127">
+        <v>20000000</v>
+      </c>
+      <c r="L127">
+        <f t="shared" si="24"/>
+        <v>234000000</v>
+      </c>
+      <c r="M127">
+        <f t="shared" si="23"/>
+        <v>126000000</v>
+      </c>
+      <c r="N127">
+        <f t="shared" si="25"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A128">
+        <v>105</v>
+      </c>
+      <c r="B128">
+        <v>1904</v>
+      </c>
+      <c r="C128" t="s">
+        <v>35</v>
+      </c>
+      <c r="F128" t="s">
+        <v>36</v>
+      </c>
+      <c r="G128">
+        <v>390000000</v>
+      </c>
+      <c r="H128">
+        <v>570000000</v>
+      </c>
+      <c r="I128">
+        <v>10000000</v>
+      </c>
+      <c r="J128">
+        <v>20000000</v>
+      </c>
+      <c r="K128">
+        <v>20000000</v>
+      </c>
+      <c r="L128">
+        <f t="shared" si="24"/>
+        <v>234000000</v>
+      </c>
+      <c r="M128">
+        <f t="shared" si="23"/>
+        <v>126000000</v>
+      </c>
+      <c r="N128">
+        <f t="shared" si="25"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A129">
+        <v>105</v>
+      </c>
+      <c r="B129">
+        <v>2001</v>
+      </c>
+      <c r="C129" t="s">
+        <v>35</v>
+      </c>
+      <c r="F129" t="s">
+        <v>36</v>
+      </c>
+      <c r="G129">
+        <v>390000000</v>
+      </c>
+      <c r="H129">
+        <v>570000000</v>
+      </c>
+      <c r="I129">
+        <v>10000000</v>
+      </c>
+      <c r="J129">
+        <v>20000000</v>
+      </c>
+      <c r="K129">
+        <v>20000000</v>
+      </c>
+      <c r="L129">
+        <f t="shared" si="24"/>
+        <v>234000000</v>
+      </c>
+      <c r="M129">
+        <f t="shared" si="23"/>
+        <v>126000000</v>
+      </c>
+      <c r="N129">
+        <f t="shared" si="25"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A130">
+        <v>105</v>
+      </c>
+      <c r="B130">
+        <v>2002</v>
+      </c>
+      <c r="C130" t="s">
+        <v>35</v>
+      </c>
+      <c r="F130" t="s">
+        <v>36</v>
+      </c>
+      <c r="G130">
+        <v>390000000</v>
+      </c>
+      <c r="H130">
+        <v>570000000</v>
+      </c>
+      <c r="I130">
+        <v>10000000</v>
+      </c>
+      <c r="J130">
+        <v>20000000</v>
+      </c>
+      <c r="K130">
+        <v>20000000</v>
+      </c>
+      <c r="L130">
+        <f t="shared" si="24"/>
+        <v>234000000</v>
+      </c>
+      <c r="M130">
+        <f t="shared" si="23"/>
+        <v>126000000</v>
+      </c>
+      <c r="N130">
+        <f t="shared" si="25"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A131">
+        <v>105</v>
+      </c>
+      <c r="B131">
+        <v>2003</v>
+      </c>
+      <c r="C131" t="s">
+        <v>35</v>
+      </c>
+      <c r="F131" t="s">
+        <v>36</v>
+      </c>
+      <c r="G131">
+        <v>390000000</v>
+      </c>
+      <c r="H131">
+        <v>570000000</v>
+      </c>
+      <c r="I131">
+        <v>10000000</v>
+      </c>
+      <c r="J131">
+        <v>20000000</v>
+      </c>
+      <c r="K131">
+        <v>20000000</v>
+      </c>
+      <c r="L131">
+        <f t="shared" si="24"/>
+        <v>234000000</v>
+      </c>
+      <c r="M131">
+        <f t="shared" si="23"/>
+        <v>126000000</v>
+      </c>
+      <c r="N131">
+        <f t="shared" si="25"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A132">
+        <v>105</v>
+      </c>
+      <c r="B132">
+        <v>2004</v>
+      </c>
+      <c r="C132" t="s">
+        <v>35</v>
+      </c>
+      <c r="F132" t="s">
+        <v>36</v>
+      </c>
+      <c r="G132">
+        <v>390000000</v>
+      </c>
+      <c r="H132">
+        <v>570000000</v>
+      </c>
+      <c r="I132">
+        <v>10000000</v>
+      </c>
+      <c r="J132">
+        <v>20000000</v>
+      </c>
+      <c r="K132">
+        <v>20000000</v>
+      </c>
+      <c r="L132">
+        <f t="shared" si="24"/>
+        <v>234000000</v>
+      </c>
+      <c r="M132">
+        <f t="shared" si="23"/>
+        <v>126000000</v>
+      </c>
+      <c r="N132">
+        <f t="shared" si="25"/>
+        <v>156000000</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A133">
+        <v>105</v>
+      </c>
+      <c r="B133">
+        <v>2101</v>
+      </c>
+      <c r="C133" t="s">
+        <v>35</v>
+      </c>
+      <c r="F133" t="s">
+        <v>36</v>
+      </c>
+      <c r="G133">
+        <v>397000000</v>
+      </c>
+      <c r="H133">
+        <v>580000000</v>
+      </c>
+      <c r="I133">
+        <v>10000000</v>
+      </c>
+      <c r="J133">
+        <v>20000000</v>
+      </c>
+      <c r="K133">
+        <v>20000000</v>
+      </c>
+      <c r="L133">
+        <f t="shared" si="24"/>
+        <v>238200000</v>
+      </c>
+      <c r="M133">
+        <f t="shared" si="23"/>
+        <v>128800000</v>
+      </c>
+      <c r="N133">
+        <f t="shared" si="25"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A134">
+        <v>105</v>
+      </c>
+      <c r="B134">
+        <v>2102</v>
+      </c>
+      <c r="C134" t="s">
+        <v>35</v>
+      </c>
+      <c r="F134" t="s">
+        <v>36</v>
+      </c>
+      <c r="G134">
+        <v>397000000</v>
+      </c>
+      <c r="H134">
+        <v>580000000</v>
+      </c>
+      <c r="I134">
+        <v>10000000</v>
+      </c>
+      <c r="J134">
+        <v>20000000</v>
+      </c>
+      <c r="K134">
+        <v>20000000</v>
+      </c>
+      <c r="L134">
+        <f t="shared" ref="L134:L145" si="26">SUM(G134*60%)</f>
+        <v>238200000</v>
+      </c>
+      <c r="M134">
+        <f t="shared" si="23"/>
+        <v>128800000</v>
+      </c>
+      <c r="N134">
+        <f t="shared" ref="N134:N145" si="27">SUM(G134-L134)</f>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A135">
+        <v>105</v>
+      </c>
+      <c r="B135">
+        <v>2103</v>
+      </c>
+      <c r="C135" t="s">
+        <v>35</v>
+      </c>
+      <c r="F135" t="s">
+        <v>36</v>
+      </c>
+      <c r="G135">
+        <v>397000000</v>
+      </c>
+      <c r="H135">
+        <v>580000000</v>
+      </c>
+      <c r="I135">
+        <v>10000000</v>
+      </c>
+      <c r="J135">
+        <v>20000000</v>
+      </c>
+      <c r="K135">
+        <v>20000000</v>
+      </c>
+      <c r="L135">
+        <f t="shared" si="26"/>
+        <v>238200000</v>
+      </c>
+      <c r="M135">
+        <f t="shared" si="23"/>
+        <v>128800000</v>
+      </c>
+      <c r="N135">
+        <f t="shared" si="27"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A136">
+        <v>105</v>
+      </c>
+      <c r="B136">
+        <v>2104</v>
+      </c>
+      <c r="C136" t="s">
+        <v>35</v>
+      </c>
+      <c r="F136" t="s">
+        <v>36</v>
+      </c>
+      <c r="G136">
+        <v>397000000</v>
+      </c>
+      <c r="H136">
+        <v>580000000</v>
+      </c>
+      <c r="I136">
+        <v>10000000</v>
+      </c>
+      <c r="J136">
+        <v>20000000</v>
+      </c>
+      <c r="K136">
+        <v>20000000</v>
+      </c>
+      <c r="L136">
+        <f t="shared" si="26"/>
+        <v>238200000</v>
+      </c>
+      <c r="M136">
+        <f t="shared" si="23"/>
+        <v>128800000</v>
+      </c>
+      <c r="N136">
+        <f t="shared" si="27"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A137">
+        <v>105</v>
+      </c>
+      <c r="B137">
+        <v>2201</v>
+      </c>
+      <c r="C137" t="s">
+        <v>35</v>
+      </c>
+      <c r="F137" t="s">
+        <v>36</v>
+      </c>
+      <c r="G137">
+        <v>397000000</v>
+      </c>
+      <c r="H137">
+        <v>580000000</v>
+      </c>
+      <c r="I137">
+        <v>10000000</v>
+      </c>
+      <c r="J137">
+        <v>20000000</v>
+      </c>
+      <c r="K137">
+        <v>20000000</v>
+      </c>
+      <c r="L137">
+        <f t="shared" si="26"/>
+        <v>238200000</v>
+      </c>
+      <c r="M137">
+        <f t="shared" si="23"/>
+        <v>128800000</v>
+      </c>
+      <c r="N137">
+        <f t="shared" si="27"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A138">
+        <v>105</v>
+      </c>
+      <c r="B138">
+        <v>2202</v>
+      </c>
+      <c r="C138" t="s">
+        <v>35</v>
+      </c>
+      <c r="F138" t="s">
+        <v>36</v>
+      </c>
+      <c r="G138">
+        <v>397000000</v>
+      </c>
+      <c r="H138">
+        <v>580000000</v>
+      </c>
+      <c r="I138">
+        <v>10000000</v>
+      </c>
+      <c r="J138">
+        <v>20000000</v>
+      </c>
+      <c r="K138">
+        <v>20000000</v>
+      </c>
+      <c r="L138">
+        <f t="shared" si="26"/>
+        <v>238200000</v>
+      </c>
+      <c r="M138">
+        <f t="shared" si="23"/>
+        <v>128800000</v>
+      </c>
+      <c r="N138">
+        <f t="shared" si="27"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A139">
+        <v>105</v>
+      </c>
+      <c r="B139">
+        <v>2203</v>
+      </c>
+      <c r="C139" t="s">
+        <v>35</v>
+      </c>
+      <c r="F139" t="s">
+        <v>36</v>
+      </c>
+      <c r="G139">
+        <v>397000000</v>
+      </c>
+      <c r="H139">
+        <v>580000000</v>
+      </c>
+      <c r="I139">
+        <v>10000000</v>
+      </c>
+      <c r="J139">
+        <v>20000000</v>
+      </c>
+      <c r="K139">
+        <v>20000000</v>
+      </c>
+      <c r="L139">
+        <f t="shared" si="26"/>
+        <v>238200000</v>
+      </c>
+      <c r="M139">
+        <f t="shared" si="23"/>
+        <v>128800000</v>
+      </c>
+      <c r="N139">
+        <f t="shared" si="27"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A140">
+        <v>105</v>
+      </c>
+      <c r="B140">
+        <v>2204</v>
+      </c>
+      <c r="C140" t="s">
+        <v>35</v>
+      </c>
+      <c r="F140" t="s">
+        <v>36</v>
+      </c>
+      <c r="G140">
+        <v>397000000</v>
+      </c>
+      <c r="H140">
+        <v>580000000</v>
+      </c>
+      <c r="I140">
+        <v>10000000</v>
+      </c>
+      <c r="J140">
+        <v>20000000</v>
+      </c>
+      <c r="K140">
+        <v>20000000</v>
+      </c>
+      <c r="L140">
+        <f t="shared" si="26"/>
+        <v>238200000</v>
+      </c>
+      <c r="M140">
+        <f t="shared" si="23"/>
+        <v>128800000</v>
+      </c>
+      <c r="N140">
+        <f t="shared" si="27"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A141">
+        <v>105</v>
+      </c>
+      <c r="B141">
+        <v>2301</v>
+      </c>
+      <c r="C141" t="s">
+        <v>35</v>
+      </c>
+      <c r="F141" t="s">
+        <v>36</v>
+      </c>
+      <c r="G141">
+        <v>397000000</v>
+      </c>
+      <c r="H141">
+        <v>580000000</v>
+      </c>
+      <c r="I141">
+        <v>10000000</v>
+      </c>
+      <c r="J141">
+        <v>20000000</v>
+      </c>
+      <c r="K141">
+        <v>20000000</v>
+      </c>
+      <c r="L141">
+        <f t="shared" si="26"/>
+        <v>238200000</v>
+      </c>
+      <c r="M141">
+        <f t="shared" si="23"/>
+        <v>128800000</v>
+      </c>
+      <c r="N141">
+        <f t="shared" si="27"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A142">
+        <v>105</v>
+      </c>
+      <c r="B142">
+        <v>2302</v>
+      </c>
+      <c r="C142" t="s">
+        <v>35</v>
+      </c>
+      <c r="F142" t="s">
+        <v>36</v>
+      </c>
+      <c r="G142">
+        <v>397000000</v>
+      </c>
+      <c r="H142">
+        <v>580000000</v>
+      </c>
+      <c r="I142">
+        <v>10000000</v>
+      </c>
+      <c r="J142">
+        <v>20000000</v>
+      </c>
+      <c r="K142">
+        <v>20000000</v>
+      </c>
+      <c r="L142">
+        <f t="shared" si="26"/>
+        <v>238200000</v>
+      </c>
+      <c r="M142">
+        <f t="shared" si="23"/>
+        <v>128800000</v>
+      </c>
+      <c r="N142">
+        <f t="shared" si="27"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A143">
+        <v>105</v>
+      </c>
+      <c r="B143">
+        <v>2303</v>
+      </c>
+      <c r="C143" t="s">
+        <v>35</v>
+      </c>
+      <c r="F143" t="s">
+        <v>36</v>
+      </c>
+      <c r="G143">
+        <v>397000000</v>
+      </c>
+      <c r="H143">
+        <v>580000000</v>
+      </c>
+      <c r="I143">
+        <v>10000000</v>
+      </c>
+      <c r="J143">
+        <v>20000000</v>
+      </c>
+      <c r="K143">
+        <v>20000000</v>
+      </c>
+      <c r="L143">
+        <f t="shared" si="26"/>
+        <v>238200000</v>
+      </c>
+      <c r="M143">
+        <f t="shared" si="23"/>
+        <v>128800000</v>
+      </c>
+      <c r="N143">
+        <f t="shared" si="27"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A144">
+        <v>105</v>
+      </c>
+      <c r="B144">
+        <v>2304</v>
+      </c>
+      <c r="C144" t="s">
+        <v>35</v>
+      </c>
+      <c r="F144" t="s">
+        <v>36</v>
+      </c>
+      <c r="G144">
+        <v>397000000</v>
+      </c>
+      <c r="H144">
+        <v>580000000</v>
+      </c>
+      <c r="I144">
+        <v>10000000</v>
+      </c>
+      <c r="J144">
+        <v>20000000</v>
+      </c>
+      <c r="K144">
+        <v>20000000</v>
+      </c>
+      <c r="L144">
+        <f t="shared" si="26"/>
+        <v>238200000</v>
+      </c>
+      <c r="M144">
+        <f t="shared" si="23"/>
+        <v>128800000</v>
+      </c>
+      <c r="N144">
+        <f t="shared" si="27"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A145">
+        <v>105</v>
+      </c>
+      <c r="B145">
+        <v>2401</v>
+      </c>
+      <c r="C145" t="s">
+        <v>35</v>
+      </c>
+      <c r="F145" t="s">
+        <v>36</v>
+      </c>
+      <c r="G145">
+        <v>397000000</v>
+      </c>
+      <c r="H145">
+        <v>595000000</v>
+      </c>
+      <c r="I145">
+        <v>10000000</v>
+      </c>
+      <c r="J145">
+        <v>20000000</v>
+      </c>
+      <c r="K145">
+        <v>20000000</v>
+      </c>
+      <c r="L145">
+        <f t="shared" si="26"/>
+        <v>238200000</v>
+      </c>
+      <c r="M145">
+        <f t="shared" si="23"/>
+        <v>128800000</v>
+      </c>
+      <c r="N145">
+        <f t="shared" si="27"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A146">
+        <v>105</v>
+      </c>
+      <c r="B146">
+        <v>2402</v>
+      </c>
+      <c r="C146" t="s">
+        <v>35</v>
+      </c>
+      <c r="F146" t="s">
+        <v>36</v>
+      </c>
+      <c r="G146">
+        <v>397000000</v>
+      </c>
+      <c r="H146">
+        <v>595000000</v>
+      </c>
+      <c r="I146">
+        <v>10000000</v>
+      </c>
+      <c r="J146">
+        <v>20000000</v>
+      </c>
+      <c r="K146">
+        <v>20000000</v>
+      </c>
+      <c r="L146">
+        <f t="shared" ref="L146:L148" si="28">SUM(G146*60%)</f>
+        <v>238200000</v>
+      </c>
+      <c r="M146">
+        <f t="shared" si="23"/>
+        <v>128800000</v>
+      </c>
+      <c r="N146">
+        <f t="shared" ref="N146:N148" si="29">SUM(G146-L146)</f>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A147">
+        <v>105</v>
+      </c>
+      <c r="B147">
+        <v>2403</v>
+      </c>
+      <c r="C147" t="s">
+        <v>35</v>
+      </c>
+      <c r="F147" t="s">
+        <v>36</v>
+      </c>
+      <c r="G147">
+        <v>397000000</v>
+      </c>
+      <c r="H147">
+        <v>595000000</v>
+      </c>
+      <c r="I147">
+        <v>10000000</v>
+      </c>
+      <c r="J147">
+        <v>20000000</v>
+      </c>
+      <c r="K147">
+        <v>20000000</v>
+      </c>
+      <c r="L147">
+        <f t="shared" si="28"/>
+        <v>238200000</v>
+      </c>
+      <c r="M147">
+        <f t="shared" si="23"/>
+        <v>128800000</v>
+      </c>
+      <c r="N147">
+        <f t="shared" si="29"/>
+        <v>158800000</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A148">
+        <v>105</v>
+      </c>
+      <c r="B148">
+        <v>2404</v>
+      </c>
+      <c r="C148" t="s">
+        <v>35</v>
+      </c>
+      <c r="F148" t="s">
+        <v>36</v>
+      </c>
+      <c r="G148">
+        <v>397000000</v>
+      </c>
+      <c r="H148">
+        <v>595000000</v>
+      </c>
+      <c r="I148">
+        <v>10000000</v>
+      </c>
+      <c r="J148">
+        <v>20000000</v>
+      </c>
+      <c r="K148">
+        <v>20000000</v>
+      </c>
+      <c r="L148">
+        <f t="shared" si="28"/>
+        <v>238200000</v>
+      </c>
+      <c r="M148">
+        <f t="shared" si="23"/>
+        <v>128800000</v>
+      </c>
+      <c r="N148">
+        <f t="shared" si="29"/>
         <v>158800000</v>
       </c>
     </row>
@@ -1767,9 +6494,100 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <cols>
+    <col min="5" max="5" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <v>101</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>102</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>103</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>104</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>105</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1777,9 +6595,69 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <cols>
+    <col min="4" max="4" width="59.19921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <v>101</v>
+      </c>
+      <c r="B2">
+        <v>103</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>105</v>
+      </c>
+      <c r="B3">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>105</v>
+      </c>
+      <c r="B4">
+        <v>202</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
